--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24882,6 +24882,75 @@
       <c r="U354" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>346.14</v>
+      </c>
+      <c r="C355" t="n">
+        <v>333.43</v>
+      </c>
+      <c r="D355" t="n">
+        <v>319.73</v>
+      </c>
+      <c r="E355" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="F355" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="G355" t="n">
+        <v>334.47</v>
+      </c>
+      <c r="H355" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="I355" t="n">
+        <v>323.53</v>
+      </c>
+      <c r="J355" t="n">
+        <v>319.44</v>
+      </c>
+      <c r="K355" t="n">
+        <v>326.48</v>
+      </c>
+      <c r="L355" t="n">
+        <v>321.67</v>
+      </c>
+      <c r="M355" t="n">
+        <v>327.87</v>
+      </c>
+      <c r="N355" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="O355" t="n">
+        <v>328.37</v>
+      </c>
+      <c r="P355" t="n">
+        <v>335.28</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="R355" t="n">
+        <v>328.74</v>
+      </c>
+      <c r="S355" t="n">
+        <v>336.81</v>
+      </c>
+      <c r="T355" t="n">
+        <v>334.32</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28559,6 +28628,16 @@
       </c>
       <c r="B366" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -28727,28 +28806,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2371212301985138</v>
+        <v>-0.234678616919488</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07267021213885028</v>
+        <v>0.07155097452277615</v>
       </c>
       <c r="M2" t="n">
-        <v>4.951554305638836</v>
+        <v>4.951568637425902</v>
       </c>
       <c r="N2" t="n">
-        <v>37.66699328955435</v>
+        <v>37.61756372957277</v>
       </c>
       <c r="O2" t="n">
-        <v>6.137344156029899</v>
+        <v>6.133315883726581</v>
       </c>
       <c r="P2" t="n">
-        <v>347.796359378638</v>
+        <v>347.7702467893666</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28805,28 +28884,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3115232092057084</v>
+        <v>-0.308718904962813</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1412956140524081</v>
+        <v>0.139483317656665</v>
       </c>
       <c r="M3" t="n">
-        <v>4.544406737439863</v>
+        <v>4.548229616809513</v>
       </c>
       <c r="N3" t="n">
-        <v>30.96264900174266</v>
+        <v>30.95028051442192</v>
       </c>
       <c r="O3" t="n">
-        <v>5.564409133209263</v>
+        <v>5.563297629501942</v>
       </c>
       <c r="P3" t="n">
-        <v>336.355430637412</v>
+        <v>336.3254514157663</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28883,28 +28962,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1155229031514926</v>
+        <v>-0.1165326340880784</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0202173115014499</v>
+        <v>0.02067017110346536</v>
       </c>
       <c r="M4" t="n">
-        <v>4.489574531331131</v>
+        <v>4.482237045495385</v>
       </c>
       <c r="N4" t="n">
-        <v>33.9535228545411</v>
+        <v>33.86734496854378</v>
       </c>
       <c r="O4" t="n">
-        <v>5.826965149590403</v>
+        <v>5.819565702743098</v>
       </c>
       <c r="P4" t="n">
-        <v>324.5987820666227</v>
+        <v>324.6095765257571</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28961,28 +29040,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.12072115223923</v>
+        <v>-0.1165334878765405</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02255228266044107</v>
+        <v>0.02105634020452107</v>
       </c>
       <c r="M5" t="n">
-        <v>4.277618234518641</v>
+        <v>4.288404184349966</v>
       </c>
       <c r="N5" t="n">
-        <v>33.15981262222387</v>
+        <v>33.23360191255484</v>
       </c>
       <c r="O5" t="n">
-        <v>5.758455749784301</v>
+        <v>5.764859227470766</v>
       </c>
       <c r="P5" t="n">
-        <v>327.6148130185961</v>
+        <v>327.5700450807288</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29039,28 +29118,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3122205202558894</v>
+        <v>-0.3070067294735241</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09536878307769414</v>
+        <v>0.09251490895028402</v>
       </c>
       <c r="M6" t="n">
-        <v>5.650549446164431</v>
+        <v>5.663634882440474</v>
       </c>
       <c r="N6" t="n">
-        <v>48.54343548164232</v>
+        <v>48.66589079113105</v>
       </c>
       <c r="O6" t="n">
-        <v>6.967311926535392</v>
+        <v>6.976094236113145</v>
       </c>
       <c r="P6" t="n">
-        <v>329.83375259421</v>
+        <v>329.7780149224238</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29117,28 +29196,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2065329280301471</v>
+        <v>-0.2002756145156687</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.045986678855645</v>
+        <v>0.04325607284572752</v>
       </c>
       <c r="M7" t="n">
-        <v>5.42075434383321</v>
+        <v>5.442127562310842</v>
       </c>
       <c r="N7" t="n">
-        <v>46.45615802456994</v>
+        <v>46.69881777316368</v>
       </c>
       <c r="O7" t="n">
-        <v>6.815875440805088</v>
+        <v>6.8336533255034</v>
       </c>
       <c r="P7" t="n">
-        <v>328.2868975582904</v>
+        <v>328.2200041785037</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29195,28 +29274,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1085354417327542</v>
+        <v>-0.1046966856715258</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01041503188240622</v>
+        <v>0.009727936979824769</v>
       </c>
       <c r="M8" t="n">
-        <v>6.080698898897744</v>
+        <v>6.08179238872232</v>
       </c>
       <c r="N8" t="n">
-        <v>58.98448485132665</v>
+        <v>58.95856708929175</v>
       </c>
       <c r="O8" t="n">
-        <v>7.680135731308832</v>
+        <v>7.678448221437177</v>
       </c>
       <c r="P8" t="n">
-        <v>318.8966060183398</v>
+        <v>318.8556004710581</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29273,28 +29352,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2879942250515296</v>
+        <v>-0.2832802074659071</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0811808644328228</v>
+        <v>0.07883684450439199</v>
       </c>
       <c r="M9" t="n">
-        <v>5.49542157750126</v>
+        <v>5.505336686492933</v>
       </c>
       <c r="N9" t="n">
-        <v>49.47047347001525</v>
+        <v>49.54354327455596</v>
       </c>
       <c r="O9" t="n">
-        <v>7.033524967611564</v>
+        <v>7.038717445284756</v>
       </c>
       <c r="P9" t="n">
-        <v>322.3144464486803</v>
+        <v>322.2640913680472</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29351,28 +29430,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1765204897306387</v>
+        <v>-0.1740491751319016</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02446357226307649</v>
+        <v>0.0239066966854844</v>
       </c>
       <c r="M10" t="n">
-        <v>6.757315692623122</v>
+        <v>6.748584015187688</v>
       </c>
       <c r="N10" t="n">
-        <v>65.23131853311143</v>
+        <v>65.10537044040558</v>
       </c>
       <c r="O10" t="n">
-        <v>8.076590774151644</v>
+        <v>8.068789899384267</v>
       </c>
       <c r="P10" t="n">
-        <v>319.46547165367</v>
+        <v>319.4390522349141</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29429,28 +29508,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1604687749043213</v>
+        <v>-0.1574393493689352</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03574987518069639</v>
+        <v>0.03456182184431089</v>
       </c>
       <c r="M11" t="n">
-        <v>4.782208554891437</v>
+        <v>4.785958015131762</v>
       </c>
       <c r="N11" t="n">
-        <v>36.46183666397092</v>
+        <v>36.44647477314471</v>
       </c>
       <c r="O11" t="n">
-        <v>6.038363740614747</v>
+        <v>6.037091582305566</v>
       </c>
       <c r="P11" t="n">
-        <v>325.0575879564952</v>
+        <v>325.0252020911546</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29507,28 +29586,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07130712947150715</v>
+        <v>-0.06854190984674623</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007513024909863719</v>
+        <v>0.006969244334367741</v>
       </c>
       <c r="M12" t="n">
-        <v>4.586246725869663</v>
+        <v>4.58780408022604</v>
       </c>
       <c r="N12" t="n">
-        <v>35.26291321747631</v>
+        <v>35.23631838023754</v>
       </c>
       <c r="O12" t="n">
-        <v>5.938258433032054</v>
+        <v>5.936018731459457</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4163298480938</v>
+        <v>318.3867684578702</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29585,28 +29664,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1124650819065593</v>
+        <v>-0.1100566153886361</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04046431429533714</v>
+        <v>0.03889008960017026</v>
       </c>
       <c r="M13" t="n">
-        <v>3.012902363343841</v>
+        <v>3.019322594129326</v>
       </c>
       <c r="N13" t="n">
-        <v>15.74586946613671</v>
+        <v>15.75678216103299</v>
       </c>
       <c r="O13" t="n">
-        <v>3.968106534121369</v>
+        <v>3.969481346603482</v>
       </c>
       <c r="P13" t="n">
-        <v>326.3450420079391</v>
+        <v>326.3192944622689</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29663,28 +29742,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01538215172051559</v>
+        <v>-0.01464854759742247</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001040458775879438</v>
+        <v>0.0009484611921596331</v>
       </c>
       <c r="M14" t="n">
-        <v>2.492942699585479</v>
+        <v>2.490436525882378</v>
       </c>
       <c r="N14" t="n">
-        <v>11.92612882397543</v>
+        <v>11.89757837271565</v>
       </c>
       <c r="O14" t="n">
-        <v>3.453422769365986</v>
+        <v>3.449286646933775</v>
       </c>
       <c r="P14" t="n">
-        <v>326.245485289282</v>
+        <v>326.2376427448568</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29741,28 +29820,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0312764506042159</v>
+        <v>-0.02869389647024514</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K15" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0030641430110252</v>
+        <v>0.002584594481705338</v>
       </c>
       <c r="M15" t="n">
-        <v>2.960327449780849</v>
+        <v>2.967159068412463</v>
       </c>
       <c r="N15" t="n">
-        <v>16.70842069974103</v>
+        <v>16.7249114437862</v>
       </c>
       <c r="O15" t="n">
-        <v>4.087593509602078</v>
+        <v>4.089610182375112</v>
       </c>
       <c r="P15" t="n">
-        <v>324.4161697257844</v>
+        <v>324.3885611084274</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29819,28 +29898,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1098231349751494</v>
+        <v>-0.1082885341921052</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K16" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02928436300904624</v>
+        <v>0.02861753827814428</v>
       </c>
       <c r="M16" t="n">
-        <v>3.461373627731494</v>
+        <v>3.459349048879711</v>
       </c>
       <c r="N16" t="n">
-        <v>20.98873241255697</v>
+        <v>20.95193073343141</v>
       </c>
       <c r="O16" t="n">
-        <v>4.581346135423186</v>
+        <v>4.577327903201978</v>
       </c>
       <c r="P16" t="n">
-        <v>335.3030784197712</v>
+        <v>335.2866728756406</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29897,28 +29976,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06286413495836018</v>
+        <v>-0.06045816917359469</v>
       </c>
       <c r="J17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00582327828214535</v>
+        <v>0.00540954260819837</v>
       </c>
       <c r="M17" t="n">
-        <v>4.540141206424171</v>
+        <v>4.540322062178507</v>
       </c>
       <c r="N17" t="n">
-        <v>35.41964681948298</v>
+        <v>35.37486890265324</v>
       </c>
       <c r="O17" t="n">
-        <v>5.951440734770278</v>
+        <v>5.947677605809955</v>
       </c>
       <c r="P17" t="n">
-        <v>330.4501023101417</v>
+        <v>330.4243814983873</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29975,28 +30054,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05462889553466392</v>
+        <v>0.05511710434614026</v>
       </c>
       <c r="J18" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K18" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004672966904698761</v>
+        <v>0.004782232047936263</v>
       </c>
       <c r="M18" t="n">
-        <v>4.573580673355437</v>
+        <v>4.563454570473081</v>
       </c>
       <c r="N18" t="n">
-        <v>33.37030900130476</v>
+        <v>33.2783186394825</v>
       </c>
       <c r="O18" t="n">
-        <v>5.776703991144497</v>
+        <v>5.768736312181594</v>
       </c>
       <c r="P18" t="n">
-        <v>326.4183593385787</v>
+        <v>326.4131401758556</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30053,28 +30132,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1364987146786641</v>
+        <v>0.1405503139427372</v>
       </c>
       <c r="J19" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K19" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01918976772770564</v>
+        <v>0.02036936685909962</v>
       </c>
       <c r="M19" t="n">
-        <v>5.784538699469336</v>
+        <v>5.790270320090744</v>
       </c>
       <c r="N19" t="n">
-        <v>49.99363176264626</v>
+        <v>50.00916243266344</v>
       </c>
       <c r="O19" t="n">
-        <v>7.070617495144696</v>
+        <v>7.071715664014175</v>
       </c>
       <c r="P19" t="n">
-        <v>325.782133412689</v>
+        <v>325.7388200694007</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30131,28 +30210,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07917924737983967</v>
+        <v>-0.07601808237268561</v>
       </c>
       <c r="J20" t="n">
+        <v>354</v>
+      </c>
+      <c r="K20" t="n">
         <v>353</v>
       </c>
-      <c r="K20" t="n">
-        <v>352</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.004689391226333939</v>
+        <v>0.004341878258667053</v>
       </c>
       <c r="M20" t="n">
-        <v>6.662940112031737</v>
+        <v>6.659448325659698</v>
       </c>
       <c r="N20" t="n">
-        <v>69.41111383635999</v>
+        <v>69.30911939781048</v>
       </c>
       <c r="O20" t="n">
-        <v>8.331333256829904</v>
+        <v>8.325209871096973</v>
       </c>
       <c r="P20" t="n">
-        <v>330.5756123077201</v>
+        <v>330.5416563118912</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30190,7 +30269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68051,6 +68130,113 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:42+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-38.72479791569299,174.60870353792447</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-38.72409061917534,174.60880103492784</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-38.72338273310254,174.6089098907486</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-38.72269024777407,174.60871829291202</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-38.721989898788756,174.60867990551955</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-38.72129189697101,174.60859561345467</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-38.720590199448615,174.6086771703382</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-38.71991463628867,174.6086536047602</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-38.71923990836793,174.60879413543984</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-38.71853699197765,174.6088092527305</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-38.717844199811495,174.60896003315494</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-38.717141988026235,174.60898476868172</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-38.71644564284468,174.6090881534231</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-38.715747798182456,174.60917046139014</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-38.71504591505963,174.60918749663867</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-38.71435252796755,174.60931506332665</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-38.71366063010494,174.60947137270975</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-38.71295683803491,174.60948370159053</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-38.712263009900134,174.60961679546423</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U355"/>
+  <dimension ref="A1:U357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24951,6 +24951,144 @@
       <c r="U355" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="C356" t="n">
+        <v>336.32</v>
+      </c>
+      <c r="D356" t="n">
+        <v>321.08</v>
+      </c>
+      <c r="E356" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="F356" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="G356" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="H356" t="n">
+        <v>322.41</v>
+      </c>
+      <c r="I356" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="J356" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="K356" t="n">
+        <v>326.42</v>
+      </c>
+      <c r="L356" t="n">
+        <v>324.35</v>
+      </c>
+      <c r="M356" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="N356" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="O356" t="n">
+        <v>329.06</v>
+      </c>
+      <c r="P356" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="R356" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="S356" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="T356" t="n">
+        <v>337.19</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>346.17</v>
+      </c>
+      <c r="C357" t="n">
+        <v>334.73</v>
+      </c>
+      <c r="D357" t="n">
+        <v>320.62</v>
+      </c>
+      <c r="E357" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="F357" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="G357" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="H357" t="n">
+        <v>322.41</v>
+      </c>
+      <c r="I357" t="n">
+        <v>322.74</v>
+      </c>
+      <c r="J357" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="K357" t="n">
+        <v>326.42</v>
+      </c>
+      <c r="L357" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="M357" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="N357" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="O357" t="n">
+        <v>328.52</v>
+      </c>
+      <c r="P357" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>333.83</v>
+      </c>
+      <c r="R357" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="S357" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="T357" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24965,7 +25103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28638,6 +28776,26 @@
       </c>
       <c r="B367" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -28806,28 +28964,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.234678616919488</v>
+        <v>-0.2287733498708784</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07155097452277615</v>
+        <v>0.06863962463022599</v>
       </c>
       <c r="M2" t="n">
-        <v>4.951568637425902</v>
+        <v>4.957236005982049</v>
       </c>
       <c r="N2" t="n">
-        <v>37.61756372957277</v>
+        <v>37.57984344640639</v>
       </c>
       <c r="O2" t="n">
-        <v>6.133315883726581</v>
+        <v>6.130240080649891</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7702467893666</v>
+        <v>347.7069568527024</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28884,28 +29042,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.308718904962813</v>
+        <v>-0.3009618612179099</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.139483317656665</v>
+        <v>0.1336530841755035</v>
       </c>
       <c r="M3" t="n">
-        <v>4.548229616809513</v>
+        <v>4.568374869499264</v>
       </c>
       <c r="N3" t="n">
-        <v>30.95028051442192</v>
+        <v>31.06969736804277</v>
       </c>
       <c r="O3" t="n">
-        <v>5.563297629501942</v>
+        <v>5.574019857162582</v>
       </c>
       <c r="P3" t="n">
-        <v>336.3254514157663</v>
+        <v>336.2423117750293</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28962,28 +29120,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1165326340880784</v>
+        <v>-0.11731134984404</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02067017110346536</v>
+        <v>0.02116484265034668</v>
       </c>
       <c r="M4" t="n">
-        <v>4.482237045495385</v>
+        <v>4.461178967956909</v>
       </c>
       <c r="N4" t="n">
-        <v>33.86734496854378</v>
+        <v>33.68029029963301</v>
       </c>
       <c r="O4" t="n">
-        <v>5.819565702743098</v>
+        <v>5.803472262329942</v>
       </c>
       <c r="P4" t="n">
-        <v>324.6095765257571</v>
+        <v>324.6179246419786</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29040,28 +29198,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1165334878765405</v>
+        <v>-0.1085510406755657</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02105634020452107</v>
+        <v>0.01834938677671449</v>
       </c>
       <c r="M5" t="n">
-        <v>4.288404184349966</v>
+        <v>4.307839416583612</v>
       </c>
       <c r="N5" t="n">
-        <v>33.23360191255484</v>
+        <v>33.35835424858401</v>
       </c>
       <c r="O5" t="n">
-        <v>5.764859227470766</v>
+        <v>5.775669160243168</v>
       </c>
       <c r="P5" t="n">
-        <v>327.5700450807288</v>
+        <v>327.4844901224743</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29118,28 +29276,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3070067294735241</v>
+        <v>-0.2989039037190014</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09251490895028402</v>
+        <v>0.08847371761731926</v>
       </c>
       <c r="M6" t="n">
-        <v>5.663634882440474</v>
+        <v>5.676467307957529</v>
       </c>
       <c r="N6" t="n">
-        <v>48.66589079113105</v>
+        <v>48.71013568220695</v>
       </c>
       <c r="O6" t="n">
-        <v>6.976094236113145</v>
+        <v>6.979264694952252</v>
       </c>
       <c r="P6" t="n">
-        <v>329.7780149224238</v>
+        <v>329.6911672958511</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29196,28 +29354,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2002756145156687</v>
+        <v>-0.1892205047468526</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04325607284572752</v>
+        <v>0.0387301897985175</v>
       </c>
       <c r="M7" t="n">
-        <v>5.442127562310842</v>
+        <v>5.475690326101664</v>
       </c>
       <c r="N7" t="n">
-        <v>46.69881777316368</v>
+        <v>47.02548868540553</v>
       </c>
       <c r="O7" t="n">
-        <v>6.8336533255034</v>
+        <v>6.857513301875946</v>
       </c>
       <c r="P7" t="n">
-        <v>328.2200041785037</v>
+        <v>328.101510999516</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29274,28 +29432,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1046966856715258</v>
+        <v>-0.09797483267953495</v>
       </c>
       <c r="J8" t="n">
+        <v>356</v>
+      </c>
+      <c r="K8" t="n">
         <v>354</v>
       </c>
-      <c r="K8" t="n">
-        <v>352</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009727936979824769</v>
+        <v>0.008590075055789348</v>
       </c>
       <c r="M8" t="n">
-        <v>6.08179238872232</v>
+        <v>6.079252625626329</v>
       </c>
       <c r="N8" t="n">
-        <v>58.95856708929175</v>
+        <v>58.84445970564794</v>
       </c>
       <c r="O8" t="n">
-        <v>7.678448221437177</v>
+        <v>7.671014255341202</v>
       </c>
       <c r="P8" t="n">
-        <v>318.8556004710581</v>
+        <v>318.7836069260564</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29352,28 +29510,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2832802074659071</v>
+        <v>-0.274871559607353</v>
       </c>
       <c r="J9" t="n">
+        <v>356</v>
+      </c>
+      <c r="K9" t="n">
         <v>354</v>
       </c>
-      <c r="K9" t="n">
-        <v>352</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.07883684450439199</v>
+        <v>0.07484411760662135</v>
       </c>
       <c r="M9" t="n">
-        <v>5.505336686492933</v>
+        <v>5.520474113898208</v>
       </c>
       <c r="N9" t="n">
-        <v>49.54354327455596</v>
+        <v>49.60632681307053</v>
       </c>
       <c r="O9" t="n">
-        <v>7.038717445284756</v>
+        <v>7.043175903885301</v>
       </c>
       <c r="P9" t="n">
-        <v>322.2640913680472</v>
+        <v>322.1740316125537</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29430,28 +29588,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1740491751319016</v>
+        <v>-0.1671396385693966</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0239066966854844</v>
+        <v>0.02224742123093226</v>
       </c>
       <c r="M10" t="n">
-        <v>6.748584015187688</v>
+        <v>6.739609562629581</v>
       </c>
       <c r="N10" t="n">
-        <v>65.10537044040558</v>
+        <v>64.96948976357201</v>
       </c>
       <c r="O10" t="n">
-        <v>8.068789899384267</v>
+        <v>8.060365361667671</v>
       </c>
       <c r="P10" t="n">
-        <v>319.4390522349141</v>
+        <v>319.3649918426835</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29508,28 +29666,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1574393493689352</v>
+        <v>-0.1515463153750073</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03456182184431089</v>
+        <v>0.03230160032509577</v>
       </c>
       <c r="M11" t="n">
-        <v>4.785958015131762</v>
+        <v>4.792269901812936</v>
       </c>
       <c r="N11" t="n">
-        <v>36.44647477314471</v>
+        <v>36.4089364832116</v>
       </c>
       <c r="O11" t="n">
-        <v>6.037091582305566</v>
+        <v>6.033981809983487</v>
       </c>
       <c r="P11" t="n">
-        <v>325.0252020911546</v>
+        <v>324.9620371582795</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29586,28 +29744,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06854190984674623</v>
+        <v>-0.06021750963135786</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006969244334367741</v>
+        <v>0.005395569458064742</v>
       </c>
       <c r="M12" t="n">
-        <v>4.58780408022604</v>
+        <v>4.606782287853274</v>
       </c>
       <c r="N12" t="n">
-        <v>35.23631838023754</v>
+        <v>35.37202552883024</v>
       </c>
       <c r="O12" t="n">
-        <v>5.936018731459457</v>
+        <v>5.9474385687311</v>
       </c>
       <c r="P12" t="n">
-        <v>318.3867684578702</v>
+        <v>318.2975426462343</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29664,28 +29822,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1100566153886361</v>
+        <v>-0.1034459521076008</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03889008960017026</v>
+        <v>0.03443457199773381</v>
       </c>
       <c r="M13" t="n">
-        <v>3.019322594129326</v>
+        <v>3.042963772795055</v>
       </c>
       <c r="N13" t="n">
-        <v>15.75678216103299</v>
+        <v>15.87871182234983</v>
       </c>
       <c r="O13" t="n">
-        <v>3.969481346603482</v>
+        <v>3.984810136298821</v>
       </c>
       <c r="P13" t="n">
-        <v>326.3192944622689</v>
+        <v>326.2484371053567</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29742,28 +29900,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01464854759742247</v>
+        <v>-0.01282683886546902</v>
       </c>
       <c r="J14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0009484611921596331</v>
+        <v>0.000734367478806619</v>
       </c>
       <c r="M14" t="n">
-        <v>2.490436525882378</v>
+        <v>2.487703437224789</v>
       </c>
       <c r="N14" t="n">
-        <v>11.89757837271565</v>
+        <v>11.84699048149993</v>
       </c>
       <c r="O14" t="n">
-        <v>3.449286646933775</v>
+        <v>3.441945740638561</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2376427448568</v>
+        <v>326.2181179575436</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29820,28 +29978,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02869389647024514</v>
+        <v>-0.0231782049830215</v>
       </c>
       <c r="J15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002584594481705338</v>
+        <v>0.001691565106590964</v>
       </c>
       <c r="M15" t="n">
-        <v>2.967159068412463</v>
+        <v>2.982600304926538</v>
       </c>
       <c r="N15" t="n">
-        <v>16.7249114437862</v>
+        <v>16.77787164761842</v>
       </c>
       <c r="O15" t="n">
-        <v>4.089610182375112</v>
+        <v>4.096080034327749</v>
       </c>
       <c r="P15" t="n">
-        <v>324.3885611084274</v>
+        <v>324.3294424169619</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29898,28 +30056,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1082885341921052</v>
+        <v>-0.1052436869353924</v>
       </c>
       <c r="J16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02861753827814428</v>
+        <v>0.02730627059237345</v>
       </c>
       <c r="M16" t="n">
-        <v>3.459349048879711</v>
+        <v>3.455132451365698</v>
       </c>
       <c r="N16" t="n">
-        <v>20.95193073343141</v>
+        <v>20.87887436828466</v>
       </c>
       <c r="O16" t="n">
-        <v>4.577327903201978</v>
+        <v>4.569340692953926</v>
       </c>
       <c r="P16" t="n">
-        <v>335.2866728756406</v>
+        <v>335.2540361767262</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29976,28 +30134,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06045816917359469</v>
+        <v>-0.0554264247594245</v>
       </c>
       <c r="J17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00540954260819837</v>
+        <v>0.004584408378064397</v>
       </c>
       <c r="M17" t="n">
-        <v>4.540322062178507</v>
+        <v>4.541725395728064</v>
       </c>
       <c r="N17" t="n">
-        <v>35.37486890265324</v>
+        <v>35.2984893211802</v>
       </c>
       <c r="O17" t="n">
-        <v>5.947677605809955</v>
+        <v>5.941253177670532</v>
       </c>
       <c r="P17" t="n">
-        <v>330.4243814983873</v>
+        <v>330.3704466244653</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30054,28 +30212,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05511710434614026</v>
+        <v>0.05647964718010464</v>
       </c>
       <c r="J18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004782232047936263</v>
+        <v>0.005073925130955836</v>
       </c>
       <c r="M18" t="n">
-        <v>4.563454570473081</v>
+        <v>4.545539102250712</v>
       </c>
       <c r="N18" t="n">
-        <v>33.2783186394825</v>
+        <v>33.10030189774579</v>
       </c>
       <c r="O18" t="n">
-        <v>5.768736312181594</v>
+        <v>5.753286182500032</v>
       </c>
       <c r="P18" t="n">
-        <v>326.4131401758556</v>
+        <v>326.3985357243267</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30132,28 +30290,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1405503139427372</v>
+        <v>0.1474479042110905</v>
       </c>
       <c r="J19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02036936685909962</v>
+        <v>0.02251081594179649</v>
       </c>
       <c r="M19" t="n">
-        <v>5.790270320090744</v>
+        <v>5.795224693056603</v>
       </c>
       <c r="N19" t="n">
-        <v>50.00916243266344</v>
+        <v>49.95732525720948</v>
       </c>
       <c r="O19" t="n">
-        <v>7.071715664014175</v>
+        <v>7.068049607721318</v>
       </c>
       <c r="P19" t="n">
-        <v>325.7388200694007</v>
+        <v>325.6648881218409</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30210,28 +30368,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07601808237268561</v>
+        <v>-0.06715917411645528</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K20" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004341878258667053</v>
+        <v>0.003410790289494536</v>
       </c>
       <c r="M20" t="n">
-        <v>6.659448325659698</v>
+        <v>6.665928428218352</v>
       </c>
       <c r="N20" t="n">
-        <v>69.30911939781048</v>
+        <v>69.29438204549396</v>
       </c>
       <c r="O20" t="n">
-        <v>8.325209871096973</v>
+        <v>8.32432472008955</v>
       </c>
       <c r="P20" t="n">
-        <v>330.5416563118912</v>
+        <v>330.4462503323101</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30269,7 +30427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U355"/>
+  <dimension ref="A1:U357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68237,6 +68395,220 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-38.72479911037202,174.60868024026436</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-38.72409232000001,174.6087678676531</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-38.723383527620605,174.6088943975398</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-38.722690647963084,174.60871048899926</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-38.72198902779327,174.60869689034064</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-38.721291402629674,174.60860525339533</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-38.720589863045866,174.60868590021502</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-38.71991485786352,174.60866268571982</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-38.71923827543561,174.60877226888775</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-38.71853704327412,174.60880993963116</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-38.7178419085913,174.60892935188804</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-38.717140551735206,174.60896553583754</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-38.716445146985535,174.60908151357685</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-38.71574720627596,174.6091625625841</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-38.7150459331094,174.60918772547546</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-38.71435252796755,174.60931506332665</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-38.71366026186939,174.60946691261816</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-38.712957697254446,174.6094941083684</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-38.71226030006956,174.609583974405</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-38.72479793334837,174.60870319362408</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-38.72409138425334,174.60878611539272</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-38.723383256896156,174.6088996767073</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-38.722689582752935,174.6087312611786</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-38.72198842162604,174.60870871085774</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-38.721291043643205,174.60861225382834</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-38.720589863045866,174.60868590021502</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-38.71991485786352,174.60866268571982</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-38.71923827543561,174.60877226888775</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-38.71853704327412,174.60880993963116</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-38.71784187439392,174.6089288939587</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-38.71714042349478,174.60896381861934</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-38.71644552315459,174.6090865507016</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-38.71574766950716,174.60916874425837</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-38.71504585188542,174.60918669570998</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-38.71435198977145,174.60930854466886</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-38.71366028075327,174.60946714134082</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-38.71295781055806,174.60949548069078</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-38.712261064865885,174.6095932374912</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U357"/>
+  <dimension ref="A1:U358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25089,6 +25089,75 @@
       <c r="U357" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>345.33</v>
+      </c>
+      <c r="C358" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="D358" t="n">
+        <v>322.52</v>
+      </c>
+      <c r="E358" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="F358" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="G358" t="n">
+        <v>329.28</v>
+      </c>
+      <c r="H358" t="n">
+        <v>320.06</v>
+      </c>
+      <c r="I358" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="J358" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="K358" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="L358" t="n">
+        <v>325.27</v>
+      </c>
+      <c r="M358" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="N358" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="O358" t="n">
+        <v>329.36</v>
+      </c>
+      <c r="P358" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="R358" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="S358" t="n">
+        <v>341.8</v>
+      </c>
+      <c r="T358" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28796,6 +28865,16 @@
       </c>
       <c r="B369" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -28964,28 +29043,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2287733498708784</v>
+        <v>-0.226831582450158</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06863962463022599</v>
+        <v>0.06784412914753124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.957236005982049</v>
+        <v>4.954196491315273</v>
       </c>
       <c r="N2" t="n">
-        <v>37.57984344640639</v>
+        <v>37.51082739000194</v>
       </c>
       <c r="O2" t="n">
-        <v>6.130240080649891</v>
+        <v>6.12460834584563</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7069568527024</v>
+        <v>347.6860237362336</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29042,28 +29121,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3009618612179099</v>
+        <v>-0.2984120124135101</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1336530841755035</v>
+        <v>0.1320943725736441</v>
       </c>
       <c r="M3" t="n">
-        <v>4.568374869499264</v>
+        <v>4.570378968872552</v>
       </c>
       <c r="N3" t="n">
-        <v>31.06969736804277</v>
+        <v>31.04517571884048</v>
       </c>
       <c r="O3" t="n">
-        <v>5.574019857162582</v>
+        <v>5.571819785208462</v>
       </c>
       <c r="P3" t="n">
-        <v>336.2423117750293</v>
+        <v>336.2148232707776</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29120,28 +29199,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.11731134984404</v>
+        <v>-0.1167885613767047</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02116484265034668</v>
+        <v>0.02109230808405016</v>
       </c>
       <c r="M4" t="n">
-        <v>4.461178967956909</v>
+        <v>4.451355990226128</v>
       </c>
       <c r="N4" t="n">
-        <v>33.68029029963301</v>
+        <v>33.58857535993938</v>
       </c>
       <c r="O4" t="n">
-        <v>5.803472262329942</v>
+        <v>5.795565145862772</v>
       </c>
       <c r="P4" t="n">
-        <v>324.6179246419786</v>
+        <v>324.612288749771</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29198,28 +29277,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1085510406755657</v>
+        <v>-0.107386357683285</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01834938677671449</v>
+        <v>0.01805518769387959</v>
       </c>
       <c r="M5" t="n">
-        <v>4.307839416583612</v>
+        <v>4.302063047534154</v>
       </c>
       <c r="N5" t="n">
-        <v>33.35835424858401</v>
+        <v>33.27795488602106</v>
       </c>
       <c r="O5" t="n">
-        <v>5.775669160243168</v>
+        <v>5.768704784093312</v>
       </c>
       <c r="P5" t="n">
-        <v>327.4844901224743</v>
+        <v>327.4719343217812</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29276,28 +29355,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2989039037190014</v>
+        <v>-0.2971865854191489</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08847371761731926</v>
+        <v>0.08794260912431895</v>
       </c>
       <c r="M6" t="n">
-        <v>5.676467307957529</v>
+        <v>5.669890409240382</v>
       </c>
       <c r="N6" t="n">
-        <v>48.71013568220695</v>
+        <v>48.60204647682014</v>
       </c>
       <c r="O6" t="n">
-        <v>6.979264694952252</v>
+        <v>6.971516798862363</v>
       </c>
       <c r="P6" t="n">
-        <v>329.6911672958511</v>
+        <v>329.6726538407373</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29354,28 +29433,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1892205047468526</v>
+        <v>-0.1859241387411789</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0387301897985175</v>
+        <v>0.03756095309929108</v>
       </c>
       <c r="M7" t="n">
-        <v>5.475690326101664</v>
+        <v>5.479215285307465</v>
       </c>
       <c r="N7" t="n">
-        <v>47.02548868540553</v>
+        <v>46.99823178782059</v>
       </c>
       <c r="O7" t="n">
-        <v>6.857513301875946</v>
+        <v>6.855525639060844</v>
       </c>
       <c r="P7" t="n">
-        <v>328.101510999516</v>
+        <v>328.065974707793</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29432,28 +29511,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09797483267953495</v>
+        <v>-0.09591040924817777</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008590075055789348</v>
+        <v>0.00827401604716882</v>
       </c>
       <c r="M8" t="n">
-        <v>6.079252625626329</v>
+        <v>6.071965279657422</v>
       </c>
       <c r="N8" t="n">
-        <v>58.84445970564794</v>
+        <v>58.71994107224174</v>
       </c>
       <c r="O8" t="n">
-        <v>7.671014255341202</v>
+        <v>7.662893779261314</v>
       </c>
       <c r="P8" t="n">
-        <v>318.7836069260564</v>
+        <v>318.7613673767723</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29510,28 +29589,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.274871559607353</v>
+        <v>-0.2707648107336729</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07484411760662135</v>
+        <v>0.07293421878534267</v>
       </c>
       <c r="M9" t="n">
-        <v>5.520474113898208</v>
+        <v>5.527476666824884</v>
       </c>
       <c r="N9" t="n">
-        <v>49.60632681307053</v>
+        <v>49.62979125726944</v>
       </c>
       <c r="O9" t="n">
-        <v>7.043175903885301</v>
+        <v>7.044841464310566</v>
       </c>
       <c r="P9" t="n">
-        <v>322.1740316125537</v>
+        <v>322.129790570437</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29588,28 +29667,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1671396385693966</v>
+        <v>-0.161577077002405</v>
       </c>
       <c r="J10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02224742123093226</v>
+        <v>0.02084037493417201</v>
       </c>
       <c r="M10" t="n">
-        <v>6.739609562629581</v>
+        <v>6.744126960104158</v>
       </c>
       <c r="N10" t="n">
-        <v>64.96948976357201</v>
+        <v>65.08498296248548</v>
       </c>
       <c r="O10" t="n">
-        <v>8.060365361667671</v>
+        <v>8.067526446345589</v>
       </c>
       <c r="P10" t="n">
-        <v>319.3649918426835</v>
+        <v>319.3050249548346</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29666,28 +29745,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1515463153750073</v>
+        <v>-0.1480752491069819</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03230160032509577</v>
+        <v>0.03095349914000123</v>
       </c>
       <c r="M11" t="n">
-        <v>4.792269901812936</v>
+        <v>4.79819015174759</v>
       </c>
       <c r="N11" t="n">
-        <v>36.4089364832116</v>
+        <v>36.42278431806986</v>
       </c>
       <c r="O11" t="n">
-        <v>6.033981809983487</v>
+        <v>6.03512918818395</v>
       </c>
       <c r="P11" t="n">
-        <v>324.9620371582795</v>
+        <v>324.9246175200239</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29744,28 +29823,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06021750963135786</v>
+        <v>-0.05562503108289125</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005395569458064742</v>
+        <v>0.00460656804529247</v>
       </c>
       <c r="M12" t="n">
-        <v>4.606782287853274</v>
+        <v>4.618618906998923</v>
       </c>
       <c r="N12" t="n">
-        <v>35.37202552883024</v>
+        <v>35.47571399507027</v>
       </c>
       <c r="O12" t="n">
-        <v>5.9474385687311</v>
+        <v>5.95614925896508</v>
       </c>
       <c r="P12" t="n">
-        <v>318.2975426462343</v>
+        <v>318.2480336848056</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29822,28 +29901,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1034459521076008</v>
+        <v>-0.09929596717087924</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03443457199773381</v>
+        <v>0.03166272852828678</v>
       </c>
       <c r="M13" t="n">
-        <v>3.042963772795055</v>
+        <v>3.059779850175367</v>
       </c>
       <c r="N13" t="n">
-        <v>15.87871182234983</v>
+        <v>15.9998113880592</v>
       </c>
       <c r="O13" t="n">
-        <v>3.984810136298821</v>
+        <v>3.999976423437918</v>
       </c>
       <c r="P13" t="n">
-        <v>326.2484371053567</v>
+        <v>326.2036984218782</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29900,28 +29979,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01282683886546902</v>
+        <v>-0.01133041533152908</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000734367478806619</v>
+        <v>0.0005752207883429339</v>
       </c>
       <c r="M14" t="n">
-        <v>2.487703437224789</v>
+        <v>2.489857710410742</v>
       </c>
       <c r="N14" t="n">
-        <v>11.84699048149993</v>
+        <v>11.83533434361228</v>
       </c>
       <c r="O14" t="n">
-        <v>3.441945740638561</v>
+        <v>3.440252075591595</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2181179575436</v>
+        <v>326.2019858462575</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29978,28 +30057,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0231782049830215</v>
+        <v>-0.02014665490816279</v>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001691565106590964</v>
+        <v>0.001278843303119892</v>
       </c>
       <c r="M15" t="n">
-        <v>2.982600304926538</v>
+        <v>2.991834515381878</v>
       </c>
       <c r="N15" t="n">
-        <v>16.77787164761842</v>
+        <v>16.81923129294281</v>
       </c>
       <c r="O15" t="n">
-        <v>4.096080034327749</v>
+        <v>4.101125612919312</v>
       </c>
       <c r="P15" t="n">
-        <v>324.3294424169619</v>
+        <v>324.2967609587599</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30056,28 +30135,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1052436869353924</v>
+        <v>-0.1026080983438829</v>
       </c>
       <c r="J16" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02730627059237345</v>
+        <v>0.02604917527693762</v>
       </c>
       <c r="M16" t="n">
-        <v>3.455132451365698</v>
+        <v>3.458448613478813</v>
       </c>
       <c r="N16" t="n">
-        <v>20.87887436828466</v>
+        <v>20.88717285723594</v>
       </c>
       <c r="O16" t="n">
-        <v>4.569340692953926</v>
+        <v>4.570248664704793</v>
       </c>
       <c r="P16" t="n">
-        <v>335.2540361767262</v>
+        <v>335.2256233594333</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30134,28 +30213,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0554264247594245</v>
+        <v>-0.05119049627638265</v>
       </c>
       <c r="J17" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004584408378064397</v>
+        <v>0.00391549879573605</v>
       </c>
       <c r="M17" t="n">
-        <v>4.541725395728064</v>
+        <v>4.551526416049388</v>
       </c>
       <c r="N17" t="n">
-        <v>35.2984893211802</v>
+        <v>35.37212078325659</v>
       </c>
       <c r="O17" t="n">
-        <v>5.941253177670532</v>
+        <v>5.947446576746747</v>
       </c>
       <c r="P17" t="n">
-        <v>330.3704466244653</v>
+        <v>330.3247814313308</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30212,28 +30291,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05647964718010464</v>
+        <v>0.05931819713774743</v>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K18" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005073925130955836</v>
+        <v>0.005611430231821757</v>
       </c>
       <c r="M18" t="n">
-        <v>4.545539102250712</v>
+        <v>4.548809969006792</v>
       </c>
       <c r="N18" t="n">
-        <v>33.10030189774579</v>
+        <v>33.08504834011962</v>
       </c>
       <c r="O18" t="n">
-        <v>5.753286182500032</v>
+        <v>5.751960391042312</v>
       </c>
       <c r="P18" t="n">
-        <v>326.3985357243267</v>
+        <v>326.3679348932323</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30290,28 +30369,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1474479042110905</v>
+        <v>0.1540442961755348</v>
       </c>
       <c r="J19" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K19" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02251081594179649</v>
+        <v>0.02445124135643162</v>
       </c>
       <c r="M19" t="n">
-        <v>5.795224693056603</v>
+        <v>5.814625540638231</v>
       </c>
       <c r="N19" t="n">
-        <v>49.95732525720948</v>
+        <v>50.23572150139713</v>
       </c>
       <c r="O19" t="n">
-        <v>7.068049607721318</v>
+        <v>7.087716240186054</v>
       </c>
       <c r="P19" t="n">
-        <v>325.6648881218409</v>
+        <v>325.5937760824729</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30368,28 +30447,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06715917411645528</v>
+        <v>-0.06045978780980273</v>
       </c>
       <c r="J20" t="n">
+        <v>357</v>
+      </c>
+      <c r="K20" t="n">
         <v>356</v>
       </c>
-      <c r="K20" t="n">
-        <v>355</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.003410790289494536</v>
+        <v>0.002764222412524719</v>
       </c>
       <c r="M20" t="n">
-        <v>6.665928428218352</v>
+        <v>6.680635755125373</v>
       </c>
       <c r="N20" t="n">
-        <v>69.29438204549396</v>
+        <v>69.52765323314013</v>
       </c>
       <c r="O20" t="n">
-        <v>8.32432472008955</v>
+        <v>8.338324366030632</v>
       </c>
       <c r="P20" t="n">
-        <v>330.4462503323101</v>
+        <v>330.3736845633678</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30427,7 +30506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U357"/>
+  <dimension ref="A1:U358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68609,6 +68688,113 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-38.72479743899709,174.6087128340349</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-38.724090430848165,174.60880470742873</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-38.72338437510427,174.60887787144998</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-38.72268706978399,174.6087802651568</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-38.72198620292611,174.6087519762435</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-38.721288842635055,174.60865517451418</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-38.72058882284903,174.60871289391244</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-38.7199148915204,174.6086640651061</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-38.7192348642182,174.6087265895487</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-38.71853616268432,174.6087981478368</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-38.71784112205114,174.60891881951324</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-38.717139089792866,174.6089459595504</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-38.71644438609752,174.6090713248474</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-38.715746948925144,174.60915912832064</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-38.715044001781145,174.60916323994195</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-38.7143491854806,174.6092745790322</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-38.7136564567587,174.6094208250074</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-38.71295212647388,174.6094266358563</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>-38.71225662714852,174.60953948872194</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U358"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25158,6 +25158,144 @@
       <c r="U358" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>344.72</v>
+      </c>
+      <c r="C359" t="n">
+        <v>332.92</v>
+      </c>
+      <c r="D359" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="E359" t="n">
+        <v>325.62</v>
+      </c>
+      <c r="F359" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="G359" t="n">
+        <v>328.68</v>
+      </c>
+      <c r="H359" t="n">
+        <v>320.38</v>
+      </c>
+      <c r="I359" t="n">
+        <v>320.55</v>
+      </c>
+      <c r="J359" t="n">
+        <v>324.48</v>
+      </c>
+      <c r="K359" t="n">
+        <v>326.84</v>
+      </c>
+      <c r="L359" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="M359" t="n">
+        <v>331.52</v>
+      </c>
+      <c r="N359" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="O359" t="n">
+        <v>329.79</v>
+      </c>
+      <c r="P359" t="n">
+        <v>337.13</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>339.41</v>
+      </c>
+      <c r="R359" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="S359" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="T359" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="C360" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="D360" t="n">
+        <v>322.66</v>
+      </c>
+      <c r="E360" t="n">
+        <v>326.22</v>
+      </c>
+      <c r="F360" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="G360" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="H360" t="n">
+        <v>322.84</v>
+      </c>
+      <c r="I360" t="n">
+        <v>320.75</v>
+      </c>
+      <c r="J360" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="K360" t="n">
+        <v>325.67</v>
+      </c>
+      <c r="L360" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="M360" t="n">
+        <v>330.48</v>
+      </c>
+      <c r="N360" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="O360" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="P360" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="R360" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="S360" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="T360" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28875,6 +29013,26 @@
       </c>
       <c r="B370" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -29043,28 +29201,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.226831582450158</v>
+        <v>-0.2234241261441834</v>
       </c>
       <c r="J2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06784412914753124</v>
+        <v>0.06654108615784271</v>
       </c>
       <c r="M2" t="n">
-        <v>4.954196491315273</v>
+        <v>4.945375384441446</v>
       </c>
       <c r="N2" t="n">
-        <v>37.51082739000194</v>
+        <v>37.35815094071669</v>
       </c>
       <c r="O2" t="n">
-        <v>6.12460834584563</v>
+        <v>6.112131456432911</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6860237362336</v>
+        <v>347.6491532205118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29121,28 +29279,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2984120124135101</v>
+        <v>-0.2929117530083702</v>
       </c>
       <c r="J3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1320943725736441</v>
+        <v>0.1285800789324026</v>
       </c>
       <c r="M3" t="n">
-        <v>4.570378968872552</v>
+        <v>4.576414498831127</v>
       </c>
       <c r="N3" t="n">
-        <v>31.04517571884048</v>
+        <v>31.02039379030711</v>
       </c>
       <c r="O3" t="n">
-        <v>5.571819785208462</v>
+        <v>5.569595478157018</v>
       </c>
       <c r="P3" t="n">
-        <v>336.2148232707776</v>
+        <v>336.1553024924535</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29199,28 +29357,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1167885613767047</v>
+        <v>-0.1157655744304143</v>
       </c>
       <c r="J4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02109230808405016</v>
+        <v>0.02095315773625916</v>
       </c>
       <c r="M4" t="n">
-        <v>4.451355990226128</v>
+        <v>4.431744163119861</v>
       </c>
       <c r="N4" t="n">
-        <v>33.58857535993938</v>
+        <v>33.40663758831987</v>
       </c>
       <c r="O4" t="n">
-        <v>5.795565145862772</v>
+        <v>5.779847540231478</v>
       </c>
       <c r="P4" t="n">
-        <v>324.612288749771</v>
+        <v>324.6012178345864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29277,28 +29435,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.107386357683285</v>
+        <v>-0.1060348349159064</v>
       </c>
       <c r="J5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01805518769387959</v>
+        <v>0.01779776142693901</v>
       </c>
       <c r="M5" t="n">
-        <v>4.302063047534154</v>
+        <v>4.285288372463205</v>
       </c>
       <c r="N5" t="n">
-        <v>33.27795488602106</v>
+        <v>33.10187411300839</v>
       </c>
       <c r="O5" t="n">
-        <v>5.768704784093312</v>
+        <v>5.753422817159224</v>
       </c>
       <c r="P5" t="n">
-        <v>327.4719343217812</v>
+        <v>327.4573062669197</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29355,28 +29513,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2971865854191489</v>
+        <v>-0.2942875697786213</v>
       </c>
       <c r="J6" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08794260912431895</v>
+        <v>0.08718719763884475</v>
       </c>
       <c r="M6" t="n">
-        <v>5.669890409240382</v>
+        <v>5.654003076990586</v>
       </c>
       <c r="N6" t="n">
-        <v>48.60204647682014</v>
+        <v>48.37185649032781</v>
       </c>
       <c r="O6" t="n">
-        <v>6.971516798862363</v>
+        <v>6.954987885706762</v>
       </c>
       <c r="P6" t="n">
-        <v>329.6726538407373</v>
+        <v>329.6412881713409</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29433,28 +29591,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1859241387411789</v>
+        <v>-0.1800910959162794</v>
       </c>
       <c r="J7" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03756095309929108</v>
+        <v>0.03557886327862647</v>
       </c>
       <c r="M7" t="n">
-        <v>5.479215285307465</v>
+        <v>5.481759705700451</v>
       </c>
       <c r="N7" t="n">
-        <v>46.99823178782059</v>
+        <v>46.9006701389122</v>
       </c>
       <c r="O7" t="n">
-        <v>6.855525639060844</v>
+        <v>6.848406394111859</v>
       </c>
       <c r="P7" t="n">
-        <v>328.065974707793</v>
+        <v>328.002865109196</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29511,28 +29669,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09591040924817777</v>
+        <v>-0.09019071980920515</v>
       </c>
       <c r="J8" t="n">
+        <v>359</v>
+      </c>
+      <c r="K8" t="n">
         <v>357</v>
       </c>
-      <c r="K8" t="n">
-        <v>355</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00827401604716882</v>
+        <v>0.007382711329594005</v>
       </c>
       <c r="M8" t="n">
-        <v>6.071965279657422</v>
+        <v>6.06527256921997</v>
       </c>
       <c r="N8" t="n">
-        <v>58.71994107224174</v>
+        <v>58.55826413498256</v>
       </c>
       <c r="O8" t="n">
-        <v>7.662893779261314</v>
+        <v>7.652337168145596</v>
       </c>
       <c r="P8" t="n">
-        <v>318.7613673767723</v>
+        <v>318.699503546411</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29589,28 +29747,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2707648107336729</v>
+        <v>-0.2647727144502469</v>
       </c>
       <c r="J9" t="n">
+        <v>359</v>
+      </c>
+      <c r="K9" t="n">
         <v>357</v>
       </c>
-      <c r="K9" t="n">
-        <v>355</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.07293421878534267</v>
+        <v>0.07045019347886505</v>
       </c>
       <c r="M9" t="n">
-        <v>5.527476666824884</v>
+        <v>5.529031912844732</v>
       </c>
       <c r="N9" t="n">
-        <v>49.62979125726944</v>
+        <v>49.52625288659641</v>
       </c>
       <c r="O9" t="n">
-        <v>7.044841464310566</v>
+        <v>7.037489103835004</v>
       </c>
       <c r="P9" t="n">
-        <v>322.129790570437</v>
+        <v>322.0650019161894</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29667,28 +29825,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.161577077002405</v>
+        <v>-0.1511474157247711</v>
       </c>
       <c r="J10" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02084037493417201</v>
+        <v>0.01833645632288361</v>
       </c>
       <c r="M10" t="n">
-        <v>6.744126960104158</v>
+        <v>6.750654347391009</v>
       </c>
       <c r="N10" t="n">
-        <v>65.08498296248548</v>
+        <v>65.24821296260416</v>
       </c>
       <c r="O10" t="n">
-        <v>8.067526446345589</v>
+        <v>8.077636595106526</v>
       </c>
       <c r="P10" t="n">
-        <v>319.3050249548346</v>
+        <v>319.1921756539572</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29745,28 +29903,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1480752491069819</v>
+        <v>-0.1425187953948309</v>
       </c>
       <c r="J11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03095349914000123</v>
+        <v>0.02893080140165261</v>
       </c>
       <c r="M11" t="n">
-        <v>4.79819015174759</v>
+        <v>4.80204294053843</v>
       </c>
       <c r="N11" t="n">
-        <v>36.42278431806986</v>
+        <v>36.37088892570581</v>
       </c>
       <c r="O11" t="n">
-        <v>6.03512918818395</v>
+        <v>6.030828212252924</v>
       </c>
       <c r="P11" t="n">
-        <v>324.9246175200239</v>
+        <v>324.8645104742865</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29823,28 +29981,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05562503108289125</v>
+        <v>-0.04592365965023829</v>
       </c>
       <c r="J12" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00460656804529247</v>
+        <v>0.003138800707459644</v>
       </c>
       <c r="M12" t="n">
-        <v>4.618618906998923</v>
+        <v>4.645322272586025</v>
       </c>
       <c r="N12" t="n">
-        <v>35.47571399507027</v>
+        <v>35.73253638840202</v>
       </c>
       <c r="O12" t="n">
-        <v>5.95614925896508</v>
+        <v>5.977669812594371</v>
       </c>
       <c r="P12" t="n">
-        <v>318.2480336848056</v>
+        <v>318.143072600949</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29901,28 +30059,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09929596717087924</v>
+        <v>-0.0914063691320512</v>
       </c>
       <c r="J13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03166272852828678</v>
+        <v>0.02675691456142559</v>
       </c>
       <c r="M13" t="n">
-        <v>3.059779850175367</v>
+        <v>3.090622896600693</v>
       </c>
       <c r="N13" t="n">
-        <v>15.9998113880592</v>
+        <v>16.2128037632445</v>
       </c>
       <c r="O13" t="n">
-        <v>3.999976423437918</v>
+        <v>4.026512605623444</v>
       </c>
       <c r="P13" t="n">
-        <v>326.2036984218782</v>
+        <v>326.1183470959342</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29979,28 +30137,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01133041533152908</v>
+        <v>-0.008256127881419942</v>
       </c>
       <c r="J14" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005752207883429339</v>
+        <v>0.0003076812277106322</v>
       </c>
       <c r="M14" t="n">
-        <v>2.489857710410742</v>
+        <v>2.49467548076538</v>
       </c>
       <c r="N14" t="n">
-        <v>11.83533434361228</v>
+        <v>11.81511879774775</v>
       </c>
       <c r="O14" t="n">
-        <v>3.440252075591595</v>
+        <v>3.437312729116708</v>
       </c>
       <c r="P14" t="n">
-        <v>326.2019858462575</v>
+        <v>326.1687260868885</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30057,28 +30215,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02014665490816279</v>
+        <v>-0.01365881429286825</v>
       </c>
       <c r="J15" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001278843303119892</v>
+        <v>0.000587578222828955</v>
       </c>
       <c r="M15" t="n">
-        <v>2.991834515381878</v>
+        <v>3.012714724126284</v>
       </c>
       <c r="N15" t="n">
-        <v>16.81923129294281</v>
+        <v>16.92875295278352</v>
       </c>
       <c r="O15" t="n">
-        <v>4.101125612919312</v>
+        <v>4.114456580495597</v>
       </c>
       <c r="P15" t="n">
-        <v>324.2967609587599</v>
+        <v>324.2265652788228</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30135,28 +30293,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1026080983438829</v>
+        <v>-0.09773440207291563</v>
       </c>
       <c r="J16" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02604917527693762</v>
+        <v>0.02381776991769036</v>
       </c>
       <c r="M16" t="n">
-        <v>3.458448613478813</v>
+        <v>3.463515875190913</v>
       </c>
       <c r="N16" t="n">
-        <v>20.88717285723594</v>
+        <v>20.88548850180197</v>
       </c>
       <c r="O16" t="n">
-        <v>4.570248664704793</v>
+        <v>4.570064387052109</v>
       </c>
       <c r="P16" t="n">
-        <v>335.2256233594333</v>
+        <v>335.1728933256355</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30213,28 +30371,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05119049627638265</v>
+        <v>-0.0396483630190376</v>
       </c>
       <c r="J17" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00391549879573605</v>
+        <v>0.002335832724055353</v>
       </c>
       <c r="M17" t="n">
-        <v>4.551526416049388</v>
+        <v>4.58780948984029</v>
       </c>
       <c r="N17" t="n">
-        <v>35.37212078325659</v>
+        <v>35.81896830859384</v>
       </c>
       <c r="O17" t="n">
-        <v>5.947446576746747</v>
+        <v>5.98489501232844</v>
       </c>
       <c r="P17" t="n">
-        <v>330.3247814313308</v>
+        <v>330.1998954381428</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30291,28 +30449,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05931819713774743</v>
+        <v>0.06935710551404774</v>
       </c>
       <c r="J18" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K18" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005611430231821757</v>
+        <v>0.007626126942630207</v>
       </c>
       <c r="M18" t="n">
-        <v>4.548809969006792</v>
+        <v>4.579295077335545</v>
       </c>
       <c r="N18" t="n">
-        <v>33.08504834011962</v>
+        <v>33.39436020011794</v>
       </c>
       <c r="O18" t="n">
-        <v>5.751960391042312</v>
+        <v>5.778785356813138</v>
       </c>
       <c r="P18" t="n">
-        <v>326.3679348932323</v>
+        <v>326.2592993074578</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30369,28 +30527,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1540442961755348</v>
+        <v>0.1685058701251976</v>
       </c>
       <c r="J19" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K19" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02445124135643162</v>
+        <v>0.02886343625791921</v>
       </c>
       <c r="M19" t="n">
-        <v>5.814625540638231</v>
+        <v>5.860439490512421</v>
       </c>
       <c r="N19" t="n">
-        <v>50.23572150139713</v>
+        <v>50.96620027529929</v>
       </c>
       <c r="O19" t="n">
-        <v>7.087716240186054</v>
+        <v>7.139061582259905</v>
       </c>
       <c r="P19" t="n">
-        <v>325.5937760824729</v>
+        <v>325.4373036735038</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30447,28 +30605,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06045978780980273</v>
+        <v>-0.04431316413585843</v>
       </c>
       <c r="J20" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002764222412524719</v>
+        <v>0.001476447365500899</v>
       </c>
       <c r="M20" t="n">
-        <v>6.680635755125373</v>
+        <v>6.722811595853354</v>
       </c>
       <c r="N20" t="n">
-        <v>69.52765323314013</v>
+        <v>70.39704876936452</v>
       </c>
       <c r="O20" t="n">
-        <v>8.338324366030632</v>
+        <v>8.39029491551784</v>
       </c>
       <c r="P20" t="n">
-        <v>330.3736845633678</v>
+        <v>330.1981352728746</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30506,7 +30664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U358"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68795,6 +68953,220 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-38.72479708000341,174.6087198348093</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-38.724090319028846,174.60880688797613</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-38.723384275054244,174.60887982244674</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-38.72268636944473,174.60879392200243</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-38.72198593220833,174.60875725530892</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-38.72128848953068,174.60866206018542</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-38.720588964493224,174.608709218175</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-38.719915472098975,174.60868785951942</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-38.719235599469584,174.60873643522046</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-38.71853668419882,174.60880513132665</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-38.71784050649732,174.60891057678526</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-38.71713886750894,174.60894298303896</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-38.71644418091407,174.60906857732488</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-38.71574658005547,174.6091542058764</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-38.71504424545369,174.60916632923818</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-38.71434672109561,174.60924473044432</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-38.7136536052742,174.60938628789242</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-38.71295117282785,174.609415085478</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>-38.71225528638646,174.6095232497332</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-38.72479732717944,174.60871501460397</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-38.724091054681516,174.60879254226944</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-38.7233844574984,174.60887626474678</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-38.72268672255717,174.60878703619795</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-38.72198592632315,174.60875737007123</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-38.72128846599037,174.60866251923017</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-38.72059005337908,174.60868096094265</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-38.71991541600463,174.60868556054226</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-38.719234958262035,174.60872784887877</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-38.71853768447952,174.60881852588935</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-38.717840677484546,174.6089128664319</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-38.717139756644166,174.60895488908483</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-38.71644438609752,174.6090713248474</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-38.71574645995832,174.6091526032201</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-38.71504429057822,174.60916690133007</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-38.714345965727034,174.60923558145225</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-38.71365141472284,174.60935975607063</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-38.712950417463844,174.60940593666373</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>-38.712252727601886,174.60949225842518</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25294,6 +25294,144 @@
         <v>345.21</v>
       </c>
       <c r="U360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>344.08</v>
+      </c>
+      <c r="C361" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="D361" t="n">
+        <v>323.36</v>
+      </c>
+      <c r="E361" t="n">
+        <v>325.87</v>
+      </c>
+      <c r="F361" t="n">
+        <v>324.03</v>
+      </c>
+      <c r="G361" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="H361" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="I361" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="J361" t="n">
+        <v>324.74</v>
+      </c>
+      <c r="K361" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="L361" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="M361" t="n">
+        <v>329.62</v>
+      </c>
+      <c r="N361" t="n">
+        <v>328</v>
+      </c>
+      <c r="O361" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="P361" t="n">
+        <v>336.03</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>338.68</v>
+      </c>
+      <c r="R361" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="S361" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="T361" t="n">
+        <v>342.36</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="C362" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="D362" t="n">
+        <v>322.72</v>
+      </c>
+      <c r="E362" t="n">
+        <v>326.51</v>
+      </c>
+      <c r="F362" t="n">
+        <v>324.48</v>
+      </c>
+      <c r="G362" t="n">
+        <v>328.62</v>
+      </c>
+      <c r="H362" t="n">
+        <v>324</v>
+      </c>
+      <c r="I362" t="n">
+        <v>324.67</v>
+      </c>
+      <c r="J362" t="n">
+        <v>324.74</v>
+      </c>
+      <c r="K362" t="n">
+        <v>328.43</v>
+      </c>
+      <c r="L362" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="M362" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="N362" t="n">
+        <v>328.56</v>
+      </c>
+      <c r="O362" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="P362" t="n">
+        <v>336.03</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>340.23</v>
+      </c>
+      <c r="R362" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="S362" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="T362" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="U362" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25310,7 +25448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29033,6 +29171,26 @@
       </c>
       <c r="B372" t="n">
         <v>0.58</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29201,28 +29359,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2234241261441834</v>
+        <v>-0.2194672096685888</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06654108615784271</v>
+        <v>0.06487396174418159</v>
       </c>
       <c r="M2" t="n">
-        <v>4.945375384441446</v>
+        <v>4.939450438228733</v>
       </c>
       <c r="N2" t="n">
-        <v>37.35815094071669</v>
+        <v>37.23875690293958</v>
       </c>
       <c r="O2" t="n">
-        <v>6.112131456432911</v>
+        <v>6.102356667955388</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6491532205118</v>
+        <v>347.6061401429895</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29279,28 +29437,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2929117530083702</v>
+        <v>-0.2876304031094516</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1285800789324026</v>
+        <v>0.1252698822670233</v>
       </c>
       <c r="M3" t="n">
-        <v>4.576414498831127</v>
+        <v>4.581026788401491</v>
       </c>
       <c r="N3" t="n">
-        <v>31.02039379030711</v>
+        <v>30.98511782608039</v>
       </c>
       <c r="O3" t="n">
-        <v>5.569595478157018</v>
+        <v>5.566427743722215</v>
       </c>
       <c r="P3" t="n">
-        <v>336.1553024924535</v>
+        <v>336.0979206829027</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29357,28 +29515,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1157655744304143</v>
+        <v>-0.1141928847615927</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02095315773625916</v>
+        <v>0.02061123878171134</v>
       </c>
       <c r="M4" t="n">
-        <v>4.431744163119861</v>
+        <v>4.41520131119432</v>
       </c>
       <c r="N4" t="n">
-        <v>33.40663758831987</v>
+        <v>33.23420324534419</v>
       </c>
       <c r="O4" t="n">
-        <v>5.779847540231478</v>
+        <v>5.764911382262887</v>
       </c>
       <c r="P4" t="n">
-        <v>324.6012178345864</v>
+        <v>324.584137941867</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29435,28 +29593,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1060348349159064</v>
+        <v>-0.104418034572954</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01779776142693901</v>
+        <v>0.01744806668205834</v>
       </c>
       <c r="M5" t="n">
-        <v>4.285288372463205</v>
+        <v>4.270057682696553</v>
       </c>
       <c r="N5" t="n">
-        <v>33.10187411300839</v>
+        <v>32.93179417217364</v>
       </c>
       <c r="O5" t="n">
-        <v>5.753422817159224</v>
+        <v>5.738623020566314</v>
       </c>
       <c r="P5" t="n">
-        <v>327.4573062669197</v>
+        <v>327.439735764309</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29513,28 +29671,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2942875697786213</v>
+        <v>-0.2917895152079145</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08718719763884475</v>
+        <v>0.08665126354161712</v>
       </c>
       <c r="M6" t="n">
-        <v>5.654003076990586</v>
+        <v>5.636043237545226</v>
       </c>
       <c r="N6" t="n">
-        <v>48.37185649032781</v>
+        <v>48.13458797800715</v>
       </c>
       <c r="O6" t="n">
-        <v>6.954987885706762</v>
+        <v>6.937909481825715</v>
       </c>
       <c r="P6" t="n">
-        <v>329.6412881713409</v>
+        <v>329.6141454163698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29591,28 +29749,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1800910959162794</v>
+        <v>-0.1752106030508595</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03557886327862647</v>
+        <v>0.03401513091240027</v>
       </c>
       <c r="M7" t="n">
-        <v>5.481759705700451</v>
+        <v>5.479147638343287</v>
       </c>
       <c r="N7" t="n">
-        <v>46.9006701389122</v>
+        <v>46.76006511935829</v>
       </c>
       <c r="O7" t="n">
-        <v>6.848406394111859</v>
+        <v>6.838133160399722</v>
       </c>
       <c r="P7" t="n">
-        <v>328.002865109196</v>
+        <v>327.94983045122</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29669,28 +29827,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09019071980920515</v>
+        <v>-0.08344804255694661</v>
       </c>
       <c r="J8" t="n">
+        <v>361</v>
+      </c>
+      <c r="K8" t="n">
         <v>359</v>
       </c>
-      <c r="K8" t="n">
-        <v>357</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.007382711329594005</v>
+        <v>0.006370503336910915</v>
       </c>
       <c r="M8" t="n">
-        <v>6.06527256921997</v>
+        <v>6.063595401183472</v>
       </c>
       <c r="N8" t="n">
-        <v>58.55826413498256</v>
+        <v>58.46436631967044</v>
       </c>
       <c r="O8" t="n">
-        <v>7.652337168145596</v>
+        <v>7.646199468995721</v>
       </c>
       <c r="P8" t="n">
-        <v>318.699503546411</v>
+        <v>318.6262754425306</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29747,28 +29905,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2647727144502469</v>
+        <v>-0.2568383466843882</v>
       </c>
       <c r="J9" t="n">
+        <v>361</v>
+      </c>
+      <c r="K9" t="n">
         <v>359</v>
       </c>
-      <c r="K9" t="n">
-        <v>357</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.07045019347886505</v>
+        <v>0.06682784066933933</v>
       </c>
       <c r="M9" t="n">
-        <v>5.529031912844732</v>
+        <v>5.541142594896156</v>
       </c>
       <c r="N9" t="n">
-        <v>49.52625288659641</v>
+        <v>49.58294146605758</v>
       </c>
       <c r="O9" t="n">
-        <v>7.037489103835004</v>
+        <v>7.041515565988445</v>
       </c>
       <c r="P9" t="n">
-        <v>322.0650019161894</v>
+        <v>321.9788217530215</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29825,28 +29983,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1511474157247711</v>
+        <v>-0.1410787760107873</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01833645632288361</v>
+        <v>0.01606543083249512</v>
       </c>
       <c r="M10" t="n">
-        <v>6.750654347391009</v>
+        <v>6.756322919398856</v>
       </c>
       <c r="N10" t="n">
-        <v>65.24821296260416</v>
+        <v>65.38127268615141</v>
       </c>
       <c r="O10" t="n">
-        <v>8.077636595106526</v>
+        <v>8.085868703247129</v>
       </c>
       <c r="P10" t="n">
-        <v>319.1921756539572</v>
+        <v>319.0827907902961</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29903,28 +30061,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1425187953948309</v>
+        <v>-0.1364279564740588</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02893080140165261</v>
+        <v>0.02671977829976069</v>
       </c>
       <c r="M11" t="n">
-        <v>4.80204294053843</v>
+        <v>4.808435805403939</v>
       </c>
       <c r="N11" t="n">
-        <v>36.37088892570581</v>
+        <v>36.36369086202436</v>
       </c>
       <c r="O11" t="n">
-        <v>6.030828212252924</v>
+        <v>6.030231410321196</v>
       </c>
       <c r="P11" t="n">
-        <v>324.8645104742865</v>
+        <v>324.7983122425554</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29981,28 +30139,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04592365965023829</v>
+        <v>-0.03764103006347152</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003138800707459644</v>
+        <v>0.002114160507036944</v>
       </c>
       <c r="M12" t="n">
-        <v>4.645322272586025</v>
+        <v>4.663945569923571</v>
       </c>
       <c r="N12" t="n">
-        <v>35.73253638840202</v>
+        <v>35.86923088462843</v>
       </c>
       <c r="O12" t="n">
-        <v>5.977669812594371</v>
+        <v>5.989092659546055</v>
       </c>
       <c r="P12" t="n">
-        <v>318.143072600949</v>
+        <v>318.0530908484546</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30059,28 +30217,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0914063691320512</v>
+        <v>-0.08454400883574831</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02675691456142559</v>
+        <v>0.02290461864948445</v>
       </c>
       <c r="M13" t="n">
-        <v>3.090622896600693</v>
+        <v>3.114878242728835</v>
       </c>
       <c r="N13" t="n">
-        <v>16.2128037632445</v>
+        <v>16.35444198074659</v>
       </c>
       <c r="O13" t="n">
-        <v>4.026512605623444</v>
+        <v>4.044062558955608</v>
       </c>
       <c r="P13" t="n">
-        <v>326.1183470959342</v>
+        <v>326.0437847229804</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30137,28 +30295,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.008256127881419942</v>
+        <v>-0.005795096299260991</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003076812277106322</v>
+        <v>0.0001528901735877719</v>
       </c>
       <c r="M14" t="n">
-        <v>2.49467548076538</v>
+        <v>2.495758090476904</v>
       </c>
       <c r="N14" t="n">
-        <v>11.81511879774775</v>
+        <v>11.77962588338712</v>
       </c>
       <c r="O14" t="n">
-        <v>3.437312729116708</v>
+        <v>3.432145958928192</v>
       </c>
       <c r="P14" t="n">
-        <v>326.1687260868885</v>
+        <v>326.1419846421728</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30215,28 +30373,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.01365881429286825</v>
+        <v>-0.008746983697348916</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000587578222828955</v>
+        <v>0.0002420063216945767</v>
       </c>
       <c r="M15" t="n">
-        <v>3.012714724126284</v>
+        <v>3.025083095221841</v>
       </c>
       <c r="N15" t="n">
-        <v>16.92875295278352</v>
+        <v>16.95278171675968</v>
       </c>
       <c r="O15" t="n">
-        <v>4.114456580495597</v>
+        <v>4.11737558606932</v>
       </c>
       <c r="P15" t="n">
-        <v>324.2265652788228</v>
+        <v>324.1732060055481</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30293,28 +30451,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09773440207291563</v>
+        <v>-0.09410426922041645</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K16" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02381776991769036</v>
+        <v>0.02229004026885162</v>
       </c>
       <c r="M16" t="n">
-        <v>3.463515875190913</v>
+        <v>3.462892898160601</v>
       </c>
       <c r="N16" t="n">
-        <v>20.88548850180197</v>
+        <v>20.83406431919137</v>
       </c>
       <c r="O16" t="n">
-        <v>4.570064387052109</v>
+        <v>4.564434720662721</v>
       </c>
       <c r="P16" t="n">
-        <v>335.1728933256355</v>
+        <v>335.133455839256</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30371,28 +30529,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0396483630190376</v>
+        <v>-0.02875998627062141</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002335832724055353</v>
+        <v>0.001223967419593408</v>
       </c>
       <c r="M17" t="n">
-        <v>4.58780948984029</v>
+        <v>4.621556069982371</v>
       </c>
       <c r="N17" t="n">
-        <v>35.81896830859384</v>
+        <v>36.20193337049849</v>
       </c>
       <c r="O17" t="n">
-        <v>5.98489501232844</v>
+        <v>6.016804248976236</v>
       </c>
       <c r="P17" t="n">
-        <v>330.1998954381428</v>
+        <v>330.0815913060488</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30449,28 +30607,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06935710551404774</v>
+        <v>0.07852842057567964</v>
       </c>
       <c r="J18" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K18" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007626126942630207</v>
+        <v>0.009742368419204062</v>
       </c>
       <c r="M18" t="n">
-        <v>4.579295077335545</v>
+        <v>4.604656149504714</v>
       </c>
       <c r="N18" t="n">
-        <v>33.39436020011794</v>
+        <v>33.61967694342459</v>
       </c>
       <c r="O18" t="n">
-        <v>5.778785356813138</v>
+        <v>5.798247747675551</v>
       </c>
       <c r="P18" t="n">
-        <v>326.2592993074578</v>
+        <v>326.1596630251142</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30527,28 +30685,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1685058701251976</v>
+        <v>0.1818904931887165</v>
       </c>
       <c r="J19" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K19" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02886343625791921</v>
+        <v>0.0332702657968974</v>
       </c>
       <c r="M19" t="n">
-        <v>5.860439490512421</v>
+        <v>5.900406988780418</v>
       </c>
       <c r="N19" t="n">
-        <v>50.96620027529929</v>
+        <v>51.56143179290092</v>
       </c>
       <c r="O19" t="n">
-        <v>7.139061582259905</v>
+        <v>7.180628927392148</v>
       </c>
       <c r="P19" t="n">
-        <v>325.4373036735038</v>
+        <v>325.2918791667275</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30605,28 +30763,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.04431316413585843</v>
+        <v>-0.02931902233379283</v>
       </c>
       <c r="J20" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K20" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001476447365500899</v>
+        <v>0.0006439588330500179</v>
       </c>
       <c r="M20" t="n">
-        <v>6.722811595853354</v>
+        <v>6.758246154645134</v>
       </c>
       <c r="N20" t="n">
-        <v>70.39704876936452</v>
+        <v>71.09655329870763</v>
       </c>
       <c r="O20" t="n">
-        <v>8.39029491551784</v>
+        <v>8.431877210841465</v>
       </c>
       <c r="P20" t="n">
-        <v>330.1981352728746</v>
+        <v>330.0344567479598</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30664,7 +30822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69167,6 +69325,220 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-38.72479670335385,174.608727179884</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-38.7240904367334,174.60880459266306</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-38.72338486946869,174.6088682312307</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-38.722686516574974,174.60879105291727</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-38.721985596753335,174.6087637967595</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-38.7212875773425,174.60867984816906</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-38.720589415983305,174.6086975017617</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-38.71991548051312,174.60868820436596</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-38.719235377184376,174.608733458622</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-38.71853800080729,174.60882276177674</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-38.71784154951874,174.60892454362994</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-38.71714049188967,174.60896473446905</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-38.71644495890094,174.6090789950145</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-38.71574755798857,174.6091672560775</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-38.715045238192836,174.60917891525997</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-38.714347410368816,174.60925307889977</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-38.713653057636925,174.60937965493684</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-38.71295223977828,174.6094280081785</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>-38.71225541857438,174.60952485076024</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-38.72479838061789,174.6086944713475</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-38.72409080750242,174.60879736242694</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-38.72338449281017,174.6088755761597</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-38.72268689322802,174.6087837080591</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-38.72198586158624,174.60875863245641</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-38.72128845422022,174.60866274875255</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-38.72059056683508,174.60866763639368</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-38.7199143165465,174.6086405005907</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-38.719235377184376,174.608733458622</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-38.7185353248405,174.6087869284599</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-38.71784154951874,174.60892454362994</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-38.71713950016298,174.6089514546485</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-38.71644448013989,174.60907258412857</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-38.71574778960409,174.60917034691468</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-38.715045238192836,174.60917891525997</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-38.714345946842805,174.60923535272744</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-38.713653057636925,174.60937965493684</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-38.71295061574696,174.60940833822747</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>-38.712253955064156,174.60950712510407</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U362"/>
+  <dimension ref="A1:U364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25423,7 +25423,7 @@
         <v>340.23</v>
       </c>
       <c r="R362" t="n">
-        <v>336.76</v>
+        <v>340.09</v>
       </c>
       <c r="S362" t="n">
         <v>343.4</v>
@@ -25434,6 +25434,144 @@
       <c r="U362" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>346.47</v>
+      </c>
+      <c r="C363" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="D363" t="n">
+        <v>322.77</v>
+      </c>
+      <c r="E363" t="n">
+        <v>327</v>
+      </c>
+      <c r="F363" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="G363" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="H363" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="I363" t="n">
+        <v>324.24</v>
+      </c>
+      <c r="J363" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="K363" t="n">
+        <v>327.62</v>
+      </c>
+      <c r="L363" t="n">
+        <v>323.9</v>
+      </c>
+      <c r="M363" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="N363" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="O363" t="n">
+        <v>328.17</v>
+      </c>
+      <c r="P363" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="R363" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="S363" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="T363" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="C364" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="D364" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="E364" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="F364" t="n">
+        <v>324.73</v>
+      </c>
+      <c r="G364" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="H364" t="n">
+        <v>323.93</v>
+      </c>
+      <c r="I364" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="J364" t="n">
+        <v>322.8</v>
+      </c>
+      <c r="K364" t="n">
+        <v>328.23</v>
+      </c>
+      <c r="L364" t="n">
+        <v>323.27</v>
+      </c>
+      <c r="M364" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="N364" t="n">
+        <v>328.03</v>
+      </c>
+      <c r="O364" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="P364" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>340.13</v>
+      </c>
+      <c r="R364" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="S364" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="T364" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25448,7 +25586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29191,6 +29329,26 @@
       </c>
       <c r="B374" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>
@@ -29359,28 +29517,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2194672096685888</v>
+        <v>-0.2147220653394516</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06487396174418159</v>
+        <v>0.06273215113771613</v>
       </c>
       <c r="M2" t="n">
-        <v>4.939450438228733</v>
+        <v>4.937680517049269</v>
       </c>
       <c r="N2" t="n">
-        <v>37.23875690293958</v>
+        <v>37.14490430688578</v>
       </c>
       <c r="O2" t="n">
-        <v>6.102356667955388</v>
+        <v>6.094661951813716</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6061401429895</v>
+        <v>347.5544058968051</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29437,28 +29595,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2876304031094516</v>
+        <v>-0.2821572426555775</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1252698822670233</v>
+        <v>0.1217671997831926</v>
       </c>
       <c r="M3" t="n">
-        <v>4.581026788401491</v>
+        <v>4.586833844052579</v>
       </c>
       <c r="N3" t="n">
-        <v>30.98511782608039</v>
+        <v>30.96236257428529</v>
       </c>
       <c r="O3" t="n">
-        <v>5.566427743722215</v>
+        <v>5.564383395694917</v>
       </c>
       <c r="P3" t="n">
-        <v>336.0979206829027</v>
+        <v>336.0382476594543</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29515,28 +29673,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1141928847615927</v>
+        <v>-0.1122375637498664</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02061123878171134</v>
+        <v>0.02012582672347996</v>
       </c>
       <c r="M4" t="n">
-        <v>4.41520131119432</v>
+        <v>4.400711515936879</v>
       </c>
       <c r="N4" t="n">
-        <v>33.23420324534419</v>
+        <v>33.07237600733588</v>
       </c>
       <c r="O4" t="n">
-        <v>5.764911382262887</v>
+        <v>5.750858719124986</v>
       </c>
       <c r="P4" t="n">
-        <v>324.584137941867</v>
+        <v>324.562811489209</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29593,28 +29751,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.104418034572954</v>
+        <v>-0.1017868386251682</v>
       </c>
       <c r="J5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01744806668205834</v>
+        <v>0.01675504368248126</v>
       </c>
       <c r="M5" t="n">
-        <v>4.270057682696553</v>
+        <v>4.26029501192412</v>
       </c>
       <c r="N5" t="n">
-        <v>32.93179417217364</v>
+        <v>32.78474177449876</v>
       </c>
       <c r="O5" t="n">
-        <v>5.738623020566314</v>
+        <v>5.725796169485844</v>
       </c>
       <c r="P5" t="n">
-        <v>327.439735764309</v>
+        <v>327.4110458591097</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29671,28 +29829,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2917895152079145</v>
+        <v>-0.2890396770376493</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K6" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08665126354161712</v>
+        <v>0.08595233226577925</v>
       </c>
       <c r="M6" t="n">
-        <v>5.636043237545226</v>
+        <v>5.619510957671345</v>
       </c>
       <c r="N6" t="n">
-        <v>48.13458797800715</v>
+        <v>47.90694296362147</v>
       </c>
       <c r="O6" t="n">
-        <v>6.937909481825715</v>
+        <v>6.921484159024095</v>
       </c>
       <c r="P6" t="n">
-        <v>329.6141454163698</v>
+        <v>329.5841618763856</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29749,28 +29907,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1752106030508595</v>
+        <v>-0.1696948563733721</v>
       </c>
       <c r="J7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03401513091240027</v>
+        <v>0.03221079426502504</v>
       </c>
       <c r="M7" t="n">
-        <v>5.479147638343287</v>
+        <v>5.480000594660051</v>
       </c>
       <c r="N7" t="n">
-        <v>46.76006511935829</v>
+        <v>46.65401769764127</v>
       </c>
       <c r="O7" t="n">
-        <v>6.838133160399722</v>
+        <v>6.830374638161604</v>
       </c>
       <c r="P7" t="n">
-        <v>327.94983045122</v>
+        <v>327.8896870115155</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29827,28 +29985,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08344804255694661</v>
+        <v>-0.07594578552444736</v>
       </c>
       <c r="J8" t="n">
+        <v>363</v>
+      </c>
+      <c r="K8" t="n">
         <v>361</v>
       </c>
-      <c r="K8" t="n">
-        <v>359</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.006370503336910915</v>
+        <v>0.00531402571638484</v>
       </c>
       <c r="M8" t="n">
-        <v>6.063595401183472</v>
+        <v>6.065366398290602</v>
       </c>
       <c r="N8" t="n">
-        <v>58.46436631967044</v>
+        <v>58.42083826764576</v>
       </c>
       <c r="O8" t="n">
-        <v>7.646199468995721</v>
+        <v>7.643352554190193</v>
       </c>
       <c r="P8" t="n">
-        <v>318.6262754425306</v>
+        <v>318.5445249399191</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29905,28 +30063,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2568383466843882</v>
+        <v>-0.2462192846825266</v>
       </c>
       <c r="J9" t="n">
+        <v>363</v>
+      </c>
+      <c r="K9" t="n">
         <v>361</v>
       </c>
-      <c r="K9" t="n">
-        <v>359</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.06682784066933933</v>
+        <v>0.06171520061875768</v>
       </c>
       <c r="M9" t="n">
-        <v>5.541142594896156</v>
+        <v>5.567661911569948</v>
       </c>
       <c r="N9" t="n">
-        <v>49.58294146605758</v>
+        <v>49.87521157443216</v>
       </c>
       <c r="O9" t="n">
-        <v>7.041515565988445</v>
+        <v>7.062238425204304</v>
       </c>
       <c r="P9" t="n">
-        <v>321.9788217530215</v>
+        <v>321.8631008807142</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29983,28 +30141,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1410787760107873</v>
+        <v>-0.1329409016298422</v>
       </c>
       <c r="J10" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K10" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01606543083249512</v>
+        <v>0.01437356196033213</v>
       </c>
       <c r="M10" t="n">
-        <v>6.756322919398856</v>
+        <v>6.754054831378516</v>
       </c>
       <c r="N10" t="n">
-        <v>65.38127268615141</v>
+        <v>65.34878710243821</v>
       </c>
       <c r="O10" t="n">
-        <v>8.085868703247129</v>
+        <v>8.083859666176684</v>
       </c>
       <c r="P10" t="n">
-        <v>319.0827907902961</v>
+        <v>318.9940682984365</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30061,28 +30219,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1364279564740588</v>
+        <v>-0.1293762030062262</v>
       </c>
       <c r="J11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02671977829976069</v>
+        <v>0.02418981636668038</v>
       </c>
       <c r="M11" t="n">
-        <v>4.808435805403939</v>
+        <v>4.820137537771293</v>
       </c>
       <c r="N11" t="n">
-        <v>36.36369086202436</v>
+        <v>36.40943414986774</v>
       </c>
       <c r="O11" t="n">
-        <v>6.030231410321196</v>
+        <v>6.034023048503191</v>
       </c>
       <c r="P11" t="n">
-        <v>324.7983122425554</v>
+        <v>324.7214241354085</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30139,28 +30297,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03764103006347152</v>
+        <v>-0.03080541836690311</v>
       </c>
       <c r="J12" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K12" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002114160507036944</v>
+        <v>0.001423237349176709</v>
       </c>
       <c r="M12" t="n">
-        <v>4.663945569923571</v>
+        <v>4.674700930188102</v>
       </c>
       <c r="N12" t="n">
-        <v>35.86923088462843</v>
+        <v>35.90299665896809</v>
       </c>
       <c r="O12" t="n">
-        <v>5.989092659546055</v>
+        <v>5.9919109355003</v>
       </c>
       <c r="P12" t="n">
-        <v>318.0530908484546</v>
+        <v>317.9785666898675</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30217,28 +30375,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08454400883574831</v>
+        <v>-0.0778835425158643</v>
       </c>
       <c r="J13" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K13" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02290461864948445</v>
+        <v>0.01945727478587078</v>
       </c>
       <c r="M13" t="n">
-        <v>3.114878242728835</v>
+        <v>3.138066218403441</v>
       </c>
       <c r="N13" t="n">
-        <v>16.35444198074659</v>
+        <v>16.48345536606111</v>
       </c>
       <c r="O13" t="n">
-        <v>4.044062558955608</v>
+        <v>4.059982187899488</v>
       </c>
       <c r="P13" t="n">
-        <v>326.0437847229804</v>
+        <v>325.9711667006823</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30295,28 +30453,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.005795096299260991</v>
+        <v>-0.003441715632116142</v>
       </c>
       <c r="J14" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K14" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001528901735877719</v>
+        <v>5.439320360045574e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.495758090476904</v>
+        <v>2.496086401834351</v>
       </c>
       <c r="N14" t="n">
-        <v>11.77962588338712</v>
+        <v>11.74232400965895</v>
       </c>
       <c r="O14" t="n">
-        <v>3.432145958928192</v>
+        <v>3.426707459013528</v>
       </c>
       <c r="P14" t="n">
-        <v>326.1419846421728</v>
+        <v>326.1163284236316</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30373,28 +30531,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.008746983697348916</v>
+        <v>-0.003991155215413614</v>
       </c>
       <c r="J15" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K15" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002420063216945767</v>
+        <v>5.060868103534677e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.025083095221841</v>
+        <v>3.036798244318788</v>
       </c>
       <c r="N15" t="n">
-        <v>16.95278171675968</v>
+        <v>16.97159227127282</v>
       </c>
       <c r="O15" t="n">
-        <v>4.11737558606932</v>
+        <v>4.11965924213069</v>
       </c>
       <c r="P15" t="n">
-        <v>324.1732060055481</v>
+        <v>324.1213500930054</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30451,28 +30609,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09410426922041645</v>
+        <v>-0.09038188064518307</v>
       </c>
       <c r="J16" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K16" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02229004026885162</v>
+        <v>0.02074943853854383</v>
       </c>
       <c r="M16" t="n">
-        <v>3.462892898160601</v>
+        <v>3.462992015638597</v>
       </c>
       <c r="N16" t="n">
-        <v>20.83406431919137</v>
+        <v>20.78847252501384</v>
       </c>
       <c r="O16" t="n">
-        <v>4.564434720662721</v>
+        <v>4.559437742201755</v>
       </c>
       <c r="P16" t="n">
-        <v>335.133455839256</v>
+        <v>335.0928666076572</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30529,28 +30687,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.02875998627062141</v>
+        <v>-0.0178373280129299</v>
       </c>
       <c r="J17" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K17" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001223967419593408</v>
+        <v>0.0004686369425825898</v>
       </c>
       <c r="M17" t="n">
-        <v>4.621556069982371</v>
+        <v>4.65625389516358</v>
       </c>
       <c r="N17" t="n">
-        <v>36.20193337049849</v>
+        <v>36.59248090426631</v>
       </c>
       <c r="O17" t="n">
-        <v>6.016804248976236</v>
+        <v>6.049171918888263</v>
       </c>
       <c r="P17" t="n">
-        <v>330.0815913060488</v>
+        <v>329.9624982469114</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30607,28 +30765,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07852842057567964</v>
+        <v>0.0921983698667684</v>
       </c>
       <c r="J18" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K18" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009742368419204062</v>
+        <v>0.01317932571568992</v>
       </c>
       <c r="M18" t="n">
-        <v>4.604656149504714</v>
+        <v>4.65531982363368</v>
       </c>
       <c r="N18" t="n">
-        <v>33.61967694342459</v>
+        <v>34.32131235971323</v>
       </c>
       <c r="O18" t="n">
-        <v>5.798247747675551</v>
+        <v>5.858439413334683</v>
       </c>
       <c r="P18" t="n">
-        <v>326.1596630251142</v>
+        <v>326.0106588223007</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30685,28 +30843,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1818904931887165</v>
+        <v>0.1934471998745801</v>
       </c>
       <c r="J19" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K19" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0332702657968974</v>
+        <v>0.0373972646071824</v>
       </c>
       <c r="M19" t="n">
-        <v>5.900406988780418</v>
+        <v>5.930314693053183</v>
       </c>
       <c r="N19" t="n">
-        <v>51.56143179290092</v>
+        <v>51.94030581209402</v>
       </c>
       <c r="O19" t="n">
-        <v>7.180628927392148</v>
+        <v>7.206962315157061</v>
       </c>
       <c r="P19" t="n">
-        <v>325.2918791667275</v>
+        <v>325.1658865318528</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30763,28 +30921,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02931902233379283</v>
+        <v>-0.01327967451755425</v>
       </c>
       <c r="J20" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K20" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0006439588330500179</v>
+        <v>0.0001312797908596952</v>
       </c>
       <c r="M20" t="n">
-        <v>6.758246154645134</v>
+        <v>6.797747221087941</v>
       </c>
       <c r="N20" t="n">
-        <v>71.09655329870763</v>
+        <v>71.96581096711587</v>
       </c>
       <c r="O20" t="n">
-        <v>8.431877210841465</v>
+        <v>8.483266526940897</v>
       </c>
       <c r="P20" t="n">
-        <v>330.0344567479598</v>
+        <v>329.8587503560165</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30822,7 +30980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U362"/>
+  <dimension ref="A1:U364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69520,7 +69678,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>-38.713653057636925,174.60937965493684</t>
+          <t>-38.71364991343629,174.60934157262463</t>
         </is>
       </c>
       <c r="S362" t="inlineStr">
@@ -69536,6 +69694,220 @@
       <c r="U362" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-38.7247981099022,174.6086997506202</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-38.72409080750242,174.60879736242694</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-38.72338452223662,174.60887500233713</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-38.722687181602716,174.608778084652</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-38.72198577919382,174.6087602391285</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-38.72128814231099,174.60866883109537</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-38.72059023043305,174.6086763662706</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-38.719914437151175,174.60864544339148</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-38.71923648006026,174.6087482271299</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-38.71853601734415,174.60879620161833</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-38.717842293311676,174.6089345035932</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-38.71714000457589,174.60895820903994</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-38.71644458273158,174.60907395788982</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-38.715747969749444,174.60917275089915</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-38.7150454277156,174.609181318046</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-38.71434676830612,174.60924530225634</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-38.7136504705178,174.609348319941</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>-38.712952050937595,174.60942572097483</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>-38.71225400227419,174.6095076968994</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-38.724797951003765,174.6087028493237</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-38.724090778076324,174.6087979362552</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-38.72338529909425,174.60885985342097</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-38.722687405240045,174.60877372364237</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-38.72198600871554,174.60875576339913</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-38.721288724933636,174.60865746973795</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-38.720590535850704,174.6086684404613</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-38.71991382290656,174.6086202695923</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-38.719237035772224,174.60875566862626</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-38.71853549582912,174.60878921812863</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-38.71784283191981,174.60894171598045</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-38.71714004732273,174.608958781446</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-38.71644493325304,174.60907865157418</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-38.71574743789161,174.60916565342123</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-38.715044741823434,174.60917262224905</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-38.714346041263916,174.60923649635146</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-38.71365023446636,174.60934546090863</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>-38.71295346724159,174.60944287500243</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>-38.71225282202212,174.60949340201586</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U364"/>
+  <dimension ref="A1:U365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25572,6 +25572,75 @@
       <c r="U364" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="C365" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="D365" t="n">
+        <v>322.54</v>
+      </c>
+      <c r="E365" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="F365" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="G365" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="H365" t="n">
+        <v>322.06</v>
+      </c>
+      <c r="I365" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="J365" t="n">
+        <v>318.6</v>
+      </c>
+      <c r="K365" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="L365" t="n">
+        <v>325.03</v>
+      </c>
+      <c r="M365" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="N365" t="n">
+        <v>326.45</v>
+      </c>
+      <c r="O365" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="P365" t="n">
+        <v>334.87</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="R365" t="n">
+        <v>336.68</v>
+      </c>
+      <c r="S365" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="T365" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29349,6 +29418,16 @@
       </c>
       <c r="B376" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -29517,28 +29596,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2147220653394516</v>
+        <v>-0.2136405159691227</v>
       </c>
       <c r="J2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06273215113771613</v>
+        <v>0.06243994993449786</v>
       </c>
       <c r="M2" t="n">
-        <v>4.937680517049269</v>
+        <v>4.929847060144857</v>
       </c>
       <c r="N2" t="n">
-        <v>37.14490430688578</v>
+        <v>37.05446877974068</v>
       </c>
       <c r="O2" t="n">
-        <v>6.094661951813716</v>
+        <v>6.087238189831303</v>
       </c>
       <c r="P2" t="n">
-        <v>347.5544058968051</v>
+        <v>347.5425656886051</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29595,28 +29674,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2821572426555775</v>
+        <v>-0.2805699021952676</v>
       </c>
       <c r="J3" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1217671997831926</v>
+        <v>0.1210567091508189</v>
       </c>
       <c r="M3" t="n">
-        <v>4.586833844052579</v>
+        <v>4.583194260604965</v>
       </c>
       <c r="N3" t="n">
-        <v>30.96236257428529</v>
+        <v>30.90231114807554</v>
       </c>
       <c r="O3" t="n">
-        <v>5.564383395694917</v>
+        <v>5.558984722777671</v>
       </c>
       <c r="P3" t="n">
-        <v>336.0382476594543</v>
+        <v>336.0208703283311</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29673,28 +29752,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1122375637498664</v>
+        <v>-0.1117373260321789</v>
       </c>
       <c r="J4" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02012582672347996</v>
+        <v>0.02005540940179473</v>
       </c>
       <c r="M4" t="n">
-        <v>4.400711515936879</v>
+        <v>4.391129594672081</v>
       </c>
       <c r="N4" t="n">
-        <v>33.07237600733588</v>
+        <v>32.98400168827592</v>
       </c>
       <c r="O4" t="n">
-        <v>5.750858719124986</v>
+        <v>5.743170003428065</v>
       </c>
       <c r="P4" t="n">
-        <v>324.562811489209</v>
+        <v>324.557335161554</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29751,28 +29830,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1017868386251682</v>
+        <v>-0.1014784713669477</v>
       </c>
       <c r="J5" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01675504368248126</v>
+        <v>0.01674409418684808</v>
       </c>
       <c r="M5" t="n">
-        <v>4.26029501192412</v>
+        <v>4.250184219529154</v>
       </c>
       <c r="N5" t="n">
-        <v>32.78474177449876</v>
+        <v>32.69561766828547</v>
       </c>
       <c r="O5" t="n">
-        <v>5.725796169485844</v>
+        <v>5.71800819064519</v>
       </c>
       <c r="P5" t="n">
-        <v>327.4110458591097</v>
+        <v>327.4076700238131</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29829,28 +29908,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2890396770376493</v>
+        <v>-0.2893891052153972</v>
       </c>
       <c r="J6" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08595233226577925</v>
+        <v>0.08656896186488183</v>
       </c>
       <c r="M6" t="n">
-        <v>5.619510957671345</v>
+        <v>5.60588314493887</v>
       </c>
       <c r="N6" t="n">
-        <v>47.90694296362147</v>
+        <v>47.77654244642182</v>
       </c>
       <c r="O6" t="n">
-        <v>6.921484159024095</v>
+        <v>6.912057757746373</v>
       </c>
       <c r="P6" t="n">
-        <v>329.5841618763856</v>
+        <v>329.5879872240664</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29907,28 +29986,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1696948563733721</v>
+        <v>-0.1674368467454549</v>
       </c>
       <c r="J7" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03221079426502504</v>
+        <v>0.03151837552744063</v>
       </c>
       <c r="M7" t="n">
-        <v>5.480000594660051</v>
+        <v>5.477549326249974</v>
       </c>
       <c r="N7" t="n">
-        <v>46.65401769764127</v>
+        <v>46.57645602868846</v>
       </c>
       <c r="O7" t="n">
-        <v>6.830374638161604</v>
+        <v>6.82469457402223</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8896870115155</v>
+        <v>327.8649675628749</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29985,28 +30064,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07594578552444736</v>
+        <v>-0.07305209495689688</v>
       </c>
       <c r="J8" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K8" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00531402571638484</v>
+        <v>0.004938276741287884</v>
       </c>
       <c r="M8" t="n">
-        <v>6.065366398290602</v>
+        <v>6.062094001758106</v>
       </c>
       <c r="N8" t="n">
-        <v>58.42083826764576</v>
+        <v>58.34308897390074</v>
       </c>
       <c r="O8" t="n">
-        <v>7.643352554190193</v>
+        <v>7.638264788150561</v>
       </c>
       <c r="P8" t="n">
-        <v>318.5445249399191</v>
+        <v>318.5128645837798</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30063,28 +30142,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2462192846825266</v>
+        <v>-0.2414612151707486</v>
       </c>
       <c r="J9" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K9" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06171520061875768</v>
+        <v>0.05954288740456704</v>
       </c>
       <c r="M9" t="n">
-        <v>5.567661911569948</v>
+        <v>5.577635946243142</v>
       </c>
       <c r="N9" t="n">
-        <v>49.87521157443216</v>
+        <v>49.96355605478096</v>
       </c>
       <c r="O9" t="n">
-        <v>7.062238425204304</v>
+        <v>7.068490366038632</v>
       </c>
       <c r="P9" t="n">
-        <v>321.8631008807142</v>
+        <v>321.811042040364</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30141,28 +30220,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1329409016298422</v>
+        <v>-0.1313013821115892</v>
       </c>
       <c r="J10" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01437356196033213</v>
+        <v>0.01409579512072368</v>
       </c>
       <c r="M10" t="n">
-        <v>6.754054831378516</v>
+        <v>6.742463410476364</v>
       </c>
       <c r="N10" t="n">
-        <v>65.34878710243821</v>
+        <v>65.1959387601369</v>
       </c>
       <c r="O10" t="n">
-        <v>8.083859666176684</v>
+        <v>8.074400210550435</v>
       </c>
       <c r="P10" t="n">
-        <v>318.9940682984365</v>
+        <v>318.976119739659</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30219,28 +30298,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1293762030062262</v>
+        <v>-0.1253903693130641</v>
       </c>
       <c r="J11" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02418981636668038</v>
+        <v>0.02278013105920418</v>
       </c>
       <c r="M11" t="n">
-        <v>4.820137537771293</v>
+        <v>4.82846514936161</v>
       </c>
       <c r="N11" t="n">
-        <v>36.40943414986774</v>
+        <v>36.4671010923102</v>
       </c>
       <c r="O11" t="n">
-        <v>6.034023048503191</v>
+        <v>6.038799640020375</v>
       </c>
       <c r="P11" t="n">
-        <v>324.7214241354085</v>
+        <v>324.6777894183329</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30297,28 +30376,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03080541836690311</v>
+        <v>-0.02668077077718591</v>
       </c>
       <c r="J12" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001423237349176709</v>
+        <v>0.001068783402955242</v>
       </c>
       <c r="M12" t="n">
-        <v>4.674700930188102</v>
+        <v>4.683711030901661</v>
       </c>
       <c r="N12" t="n">
-        <v>35.90299665896809</v>
+        <v>35.97323006045382</v>
       </c>
       <c r="O12" t="n">
-        <v>5.9919109355003</v>
+        <v>5.99776875683398</v>
       </c>
       <c r="P12" t="n">
-        <v>317.9785666898675</v>
+        <v>317.93341231453</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30375,28 +30454,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0778835425158643</v>
+        <v>-0.07547028777554338</v>
       </c>
       <c r="J13" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K13" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01945727478587078</v>
+        <v>0.0183264289516607</v>
       </c>
       <c r="M13" t="n">
-        <v>3.138066218403441</v>
+        <v>3.14411231620236</v>
       </c>
       <c r="N13" t="n">
-        <v>16.48345536606111</v>
+        <v>16.49597809310391</v>
       </c>
       <c r="O13" t="n">
-        <v>4.059982187899488</v>
+        <v>4.061524109629772</v>
       </c>
       <c r="P13" t="n">
-        <v>325.9711667006823</v>
+        <v>325.9447477138575</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30453,28 +30532,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.003441715632116142</v>
+        <v>-0.003218051334295138</v>
       </c>
       <c r="J14" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K14" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L14" t="n">
-        <v>5.439320360045574e-05</v>
+        <v>4.78106075028073e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.496086401834351</v>
+        <v>2.490553135096551</v>
       </c>
       <c r="N14" t="n">
-        <v>11.74232400965895</v>
+        <v>11.71056143237017</v>
       </c>
       <c r="O14" t="n">
-        <v>3.426707459013528</v>
+        <v>3.422069758548206</v>
       </c>
       <c r="P14" t="n">
-        <v>326.1163284236316</v>
+        <v>326.1138798698016</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30531,28 +30610,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.003991155215413614</v>
+        <v>-0.00216812876354378</v>
       </c>
       <c r="J15" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K15" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L15" t="n">
-        <v>5.060868103534677e-05</v>
+        <v>1.498742265593211e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.036798244318788</v>
+        <v>3.03936217068433</v>
       </c>
       <c r="N15" t="n">
-        <v>16.97159227127282</v>
+        <v>16.95795529408482</v>
       </c>
       <c r="O15" t="n">
-        <v>4.11965924213069</v>
+        <v>4.118003799668575</v>
       </c>
       <c r="P15" t="n">
-        <v>324.1213500930054</v>
+        <v>324.101392601155</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30609,28 +30688,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09038188064518307</v>
+        <v>-0.08924129791469461</v>
       </c>
       <c r="J16" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K16" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02074943853854383</v>
+        <v>0.02033517120156481</v>
       </c>
       <c r="M16" t="n">
-        <v>3.462992015638597</v>
+        <v>3.45932765440891</v>
       </c>
       <c r="N16" t="n">
-        <v>20.78847252501384</v>
+        <v>20.74427434018601</v>
       </c>
       <c r="O16" t="n">
-        <v>4.559437742201755</v>
+        <v>4.554588273399255</v>
       </c>
       <c r="P16" t="n">
-        <v>335.0928666076572</v>
+        <v>335.0803801346688</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30687,28 +30766,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0178373280129299</v>
+        <v>-0.01447662404961482</v>
       </c>
       <c r="J17" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K17" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0004686369425825898</v>
+        <v>0.0003094622857561236</v>
       </c>
       <c r="M17" t="n">
-        <v>4.65625389516358</v>
+        <v>4.66177564893507</v>
       </c>
       <c r="N17" t="n">
-        <v>36.59248090426631</v>
+        <v>36.60405948960531</v>
       </c>
       <c r="O17" t="n">
-        <v>6.049171918888263</v>
+        <v>6.050128882065679</v>
       </c>
       <c r="P17" t="n">
-        <v>329.9624982469114</v>
+        <v>329.9257071066123</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30765,28 +30844,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0921983698667684</v>
+        <v>0.09650669590536806</v>
       </c>
       <c r="J18" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K18" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01317932571568992</v>
+        <v>0.01442254203095983</v>
       </c>
       <c r="M18" t="n">
-        <v>4.65531982363368</v>
+        <v>4.666501681986913</v>
       </c>
       <c r="N18" t="n">
-        <v>34.32131235971323</v>
+        <v>34.41126595937007</v>
       </c>
       <c r="O18" t="n">
-        <v>5.858439413334683</v>
+        <v>5.866111655890133</v>
       </c>
       <c r="P18" t="n">
-        <v>326.0106588223007</v>
+        <v>325.9634936362353</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30843,28 +30922,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1934471998745801</v>
+        <v>0.1977342724835539</v>
       </c>
       <c r="J19" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K19" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373972646071824</v>
+        <v>0.03907971963318346</v>
       </c>
       <c r="M19" t="n">
-        <v>5.930314693053183</v>
+        <v>5.937308031599542</v>
       </c>
       <c r="N19" t="n">
-        <v>51.94030581209402</v>
+        <v>51.98004228748277</v>
       </c>
       <c r="O19" t="n">
-        <v>7.206962315157061</v>
+        <v>7.20971859974318</v>
       </c>
       <c r="P19" t="n">
-        <v>325.1658865318528</v>
+        <v>325.1189540166563</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30921,28 +31000,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01327967451755425</v>
+        <v>-0.005436763103660187</v>
       </c>
       <c r="J20" t="n">
+        <v>364</v>
+      </c>
+      <c r="K20" t="n">
         <v>363</v>
       </c>
-      <c r="K20" t="n">
-        <v>362</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0001312797908596952</v>
+        <v>2.194151454815163e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>6.797747221087941</v>
+        <v>6.816457878373106</v>
       </c>
       <c r="N20" t="n">
-        <v>71.96581096711587</v>
+        <v>72.37303650374938</v>
       </c>
       <c r="O20" t="n">
-        <v>8.483266526940897</v>
+        <v>8.507234362808479</v>
       </c>
       <c r="P20" t="n">
-        <v>329.8587503560165</v>
+        <v>329.7724873755402</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30980,7 +31059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U364"/>
+  <dimension ref="A1:U365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69911,6 +69990,113 @@
         </is>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-38.72479661507655,174.6087289013859</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-38.72408953629249,174.60882215180766</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-38.72338438687487,174.60887764192097</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-38.72268618111794,174.60879759443148</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-38.72198396655461,174.60879558591287</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-38.721287912792654,174.60867330678158</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-38.72058970812333,174.60868992055302</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-38.71991438666552,174.6086433743121</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-38.71924062651487,174.60880375214364</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-38.71853492301705,174.6087815477384</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-38.71784132723561,174.60892156708925</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-38.71714144086812,174.6089774418839</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-38.716446284041275,174.60909673943132</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-38.71574854449856,174.60918042075443</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-38.71504628507989,174.60919218779244</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-38.71435003526676,174.60928487164912</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-38.71365313317313,174.60938056982727</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>-38.712955261223016,174.60946460343825</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>-38.71225350184754,174.60950163586875</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
